--- a/BaseInflação.xlsx
+++ b/BaseInflação.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://osborne1-my.sharepoint.com/personal/antonio_macedo_osborne_com_br/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="13_ncr:1_{6FEE0F3F-AAF6-4BEC-810F-C57612871236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFB5F2BB-E3A9-410B-9624-A3A6D436D94C}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="13_ncr:1_{6FEE0F3F-AAF6-4BEC-810F-C57612871236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06D55776-F77F-4DC9-B550-A67FBCA15BA5}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3979" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3974" uniqueCount="51">
   <si>
     <t>INSUMOCDG</t>
   </si>
@@ -530,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I795"/>
+  <dimension ref="A1:I794"/>
   <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="1" customWidth="1"/>
@@ -582,7 +582,7 @@
         <v>36</v>
       </c>
       <c r="C2" s="2">
-        <v>52.25</v>
+        <v>6.2</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>37</v>
@@ -611,7 +611,7 @@
         <v>36</v>
       </c>
       <c r="C3" s="2">
-        <v>52.25</v>
+        <v>6.2</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>37</v>
@@ -640,7 +640,7 @@
         <v>36</v>
       </c>
       <c r="C4" s="2">
-        <v>52.25</v>
+        <v>6.2</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>37</v>
@@ -10558,7 +10558,7 @@
         <v>36</v>
       </c>
       <c r="C346" s="2">
-        <v>6.02</v>
+        <v>49.81</v>
       </c>
       <c r="D346" s="1" t="s">
         <v>37</v>
@@ -10587,7 +10587,7 @@
         <v>36</v>
       </c>
       <c r="C347" s="2">
-        <v>6.02</v>
+        <v>49.81</v>
       </c>
       <c r="D347" s="1" t="s">
         <v>37</v>
@@ -10616,7 +10616,7 @@
         <v>36</v>
       </c>
       <c r="C348" s="2">
-        <v>6.02</v>
+        <v>52.25</v>
       </c>
       <c r="D348" s="1" t="s">
         <v>37</v>
@@ -10645,7 +10645,7 @@
         <v>36</v>
       </c>
       <c r="C349" s="2">
-        <v>6.02</v>
+        <v>43.48</v>
       </c>
       <c r="D349" s="1" t="s">
         <v>37</v>
@@ -10674,7 +10674,7 @@
         <v>36</v>
       </c>
       <c r="C350" s="2">
-        <v>6.32</v>
+        <v>49.81</v>
       </c>
       <c r="D350" s="1" t="s">
         <v>37</v>
@@ -10703,7 +10703,7 @@
         <v>36</v>
       </c>
       <c r="C351" s="2">
-        <v>6.32</v>
+        <v>49.81</v>
       </c>
       <c r="D351" s="1" t="s">
         <v>37</v>
@@ -10732,7 +10732,7 @@
         <v>27</v>
       </c>
       <c r="C352" s="2">
-        <v>6.32</v>
+        <v>52.25</v>
       </c>
       <c r="D352" s="1" t="s">
         <v>28</v>
@@ -10761,7 +10761,7 @@
         <v>27</v>
       </c>
       <c r="C353" s="2">
-        <v>6.42</v>
+        <v>55.26</v>
       </c>
       <c r="D353" s="1" t="s">
         <v>28</v>
@@ -12466,31 +12466,31 @@
     </row>
     <row r="412" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C412" s="2">
-        <v>134.5</v>
+        <v>4.8</v>
       </c>
       <c r="D412" s="1" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E412" s="2">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="F412" s="3">
-        <v>46275</v>
+        <v>45660</v>
       </c>
       <c r="G412" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H412" s="1" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I412" s="4">
-        <v>2606</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="413" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12519,7 +12519,7 @@
         <v>13</v>
       </c>
       <c r="I413" s="4">
-        <v>2317</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="414" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12539,7 +12539,7 @@
         <v>100</v>
       </c>
       <c r="F414" s="3">
-        <v>45660</v>
+        <v>45664</v>
       </c>
       <c r="G414" s="1" t="s">
         <v>12</v>
@@ -12548,7 +12548,7 @@
         <v>13</v>
       </c>
       <c r="I414" s="4">
-        <v>2413</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="415" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12565,10 +12565,10 @@
         <v>11</v>
       </c>
       <c r="E415" s="2">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F415" s="3">
-        <v>45664</v>
+        <v>45671</v>
       </c>
       <c r="G415" s="1" t="s">
         <v>12</v>
@@ -12577,7 +12577,7 @@
         <v>13</v>
       </c>
       <c r="I415" s="4">
-        <v>2412</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="416" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12594,10 +12594,10 @@
         <v>11</v>
       </c>
       <c r="E416" s="2">
-        <v>10</v>
+        <v>279.16666700000002</v>
       </c>
       <c r="F416" s="3">
-        <v>45671</v>
+        <v>45672</v>
       </c>
       <c r="G416" s="1" t="s">
         <v>12</v>
@@ -12606,7 +12606,7 @@
         <v>13</v>
       </c>
       <c r="I416" s="4">
-        <v>2306</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="417" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12623,10 +12623,10 @@
         <v>11</v>
       </c>
       <c r="E417" s="2">
-        <v>279.16666700000002</v>
+        <v>50</v>
       </c>
       <c r="F417" s="3">
-        <v>45672</v>
+        <v>45684</v>
       </c>
       <c r="G417" s="1" t="s">
         <v>12</v>
@@ -12652,10 +12652,10 @@
         <v>11</v>
       </c>
       <c r="E418" s="2">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F418" s="3">
-        <v>45684</v>
+        <v>45686</v>
       </c>
       <c r="G418" s="1" t="s">
         <v>12</v>
@@ -12664,7 +12664,7 @@
         <v>13</v>
       </c>
       <c r="I418" s="4">
-        <v>2407</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="419" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12681,10 +12681,10 @@
         <v>11</v>
       </c>
       <c r="E419" s="2">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F419" s="3">
-        <v>45686</v>
+        <v>45688</v>
       </c>
       <c r="G419" s="1" t="s">
         <v>12</v>
@@ -12693,7 +12693,7 @@
         <v>13</v>
       </c>
       <c r="I419" s="4">
-        <v>2413</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="420" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12713,7 +12713,7 @@
         <v>300</v>
       </c>
       <c r="F420" s="3">
-        <v>45688</v>
+        <v>45693</v>
       </c>
       <c r="G420" s="1" t="s">
         <v>12</v>
@@ -12739,10 +12739,10 @@
         <v>11</v>
       </c>
       <c r="E421" s="2">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F421" s="3">
-        <v>45693</v>
+        <v>45694</v>
       </c>
       <c r="G421" s="1" t="s">
         <v>12</v>
@@ -12751,7 +12751,7 @@
         <v>13</v>
       </c>
       <c r="I421" s="4">
-        <v>2407</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="422" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12768,10 +12768,10 @@
         <v>11</v>
       </c>
       <c r="E422" s="2">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="F422" s="3">
-        <v>45694</v>
+        <v>45699</v>
       </c>
       <c r="G422" s="1" t="s">
         <v>12</v>
@@ -12780,7 +12780,7 @@
         <v>13</v>
       </c>
       <c r="I422" s="4">
-        <v>2411</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="423" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12797,7 +12797,7 @@
         <v>11</v>
       </c>
       <c r="E423" s="2">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="F423" s="3">
         <v>45699</v>
@@ -12809,7 +12809,7 @@
         <v>13</v>
       </c>
       <c r="I423" s="4">
-        <v>2412</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="424" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12826,10 +12826,10 @@
         <v>11</v>
       </c>
       <c r="E424" s="2">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="F424" s="3">
-        <v>45699</v>
+        <v>45706</v>
       </c>
       <c r="G424" s="1" t="s">
         <v>12</v>
@@ -12838,7 +12838,7 @@
         <v>13</v>
       </c>
       <c r="I424" s="4">
-        <v>2503</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="425" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12855,7 +12855,7 @@
         <v>11</v>
       </c>
       <c r="E425" s="2">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="F425" s="3">
         <v>45706</v>
@@ -12867,7 +12867,7 @@
         <v>13</v>
       </c>
       <c r="I425" s="4">
-        <v>2411</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="426" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12884,10 +12884,10 @@
         <v>11</v>
       </c>
       <c r="E426" s="2">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="F426" s="3">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G426" s="1" t="s">
         <v>12</v>
@@ -12896,7 +12896,7 @@
         <v>13</v>
       </c>
       <c r="I426" s="4">
-        <v>2413</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="427" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12913,10 +12913,10 @@
         <v>11</v>
       </c>
       <c r="E427" s="2">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="F427" s="3">
-        <v>45709</v>
+        <v>45716</v>
       </c>
       <c r="G427" s="1" t="s">
         <v>12</v>
@@ -12925,7 +12925,7 @@
         <v>13</v>
       </c>
       <c r="I427" s="4">
-        <v>2411</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="428" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12945,7 +12945,7 @@
         <v>300</v>
       </c>
       <c r="F428" s="3">
-        <v>45716</v>
+        <v>45722</v>
       </c>
       <c r="G428" s="1" t="s">
         <v>12</v>
@@ -12954,7 +12954,7 @@
         <v>13</v>
       </c>
       <c r="I428" s="4">
-        <v>2503</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="429" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12965,16 +12965,16 @@
         <v>18</v>
       </c>
       <c r="C429" s="2">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="D429" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E429" s="2">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F429" s="3">
-        <v>45722</v>
+        <v>45730</v>
       </c>
       <c r="G429" s="1" t="s">
         <v>12</v>
@@ -12983,7 +12983,7 @@
         <v>13</v>
       </c>
       <c r="I429" s="4">
-        <v>2407</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="430" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13000,7 +13000,7 @@
         <v>11</v>
       </c>
       <c r="E430" s="2">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F430" s="3">
         <v>45730</v>
@@ -13012,7 +13012,7 @@
         <v>13</v>
       </c>
       <c r="I430" s="4">
-        <v>2317</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="431" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13032,7 +13032,7 @@
         <v>500</v>
       </c>
       <c r="F431" s="3">
-        <v>45730</v>
+        <v>45733</v>
       </c>
       <c r="G431" s="1" t="s">
         <v>12</v>
@@ -13041,7 +13041,7 @@
         <v>13</v>
       </c>
       <c r="I431" s="4">
-        <v>2413</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="432" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13058,10 +13058,10 @@
         <v>11</v>
       </c>
       <c r="E432" s="2">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F432" s="3">
-        <v>45733</v>
+        <v>45737</v>
       </c>
       <c r="G432" s="1" t="s">
         <v>12</v>
@@ -13070,7 +13070,7 @@
         <v>13</v>
       </c>
       <c r="I432" s="4">
-        <v>2407</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="433" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13090,7 +13090,7 @@
         <v>200</v>
       </c>
       <c r="F433" s="3">
-        <v>45737</v>
+        <v>45743</v>
       </c>
       <c r="G433" s="1" t="s">
         <v>12</v>
@@ -13116,10 +13116,10 @@
         <v>11</v>
       </c>
       <c r="E434" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F434" s="3">
-        <v>45743</v>
+        <v>45747</v>
       </c>
       <c r="G434" s="1" t="s">
         <v>12</v>
@@ -13128,7 +13128,7 @@
         <v>13</v>
       </c>
       <c r="I434" s="4">
-        <v>2503</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="435" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13148,7 +13148,7 @@
         <v>100</v>
       </c>
       <c r="F435" s="3">
-        <v>45747</v>
+        <v>45751</v>
       </c>
       <c r="G435" s="1" t="s">
         <v>12</v>
@@ -13157,7 +13157,7 @@
         <v>13</v>
       </c>
       <c r="I435" s="4">
-        <v>2412</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="436" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13174,10 +13174,10 @@
         <v>11</v>
       </c>
       <c r="E436" s="2">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="F436" s="3">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="G436" s="1" t="s">
         <v>12</v>
@@ -13186,7 +13186,7 @@
         <v>13</v>
       </c>
       <c r="I436" s="4">
-        <v>2503</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="437" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13203,7 +13203,7 @@
         <v>11</v>
       </c>
       <c r="E437" s="2">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="F437" s="3">
         <v>45754</v>
@@ -13215,7 +13215,7 @@
         <v>13</v>
       </c>
       <c r="I437" s="4">
-        <v>2317</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="438" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13232,7 +13232,7 @@
         <v>11</v>
       </c>
       <c r="E438" s="2">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="F438" s="3">
         <v>45754</v>
@@ -13244,7 +13244,7 @@
         <v>13</v>
       </c>
       <c r="I438" s="4">
-        <v>2407</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="439" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13261,10 +13261,10 @@
         <v>11</v>
       </c>
       <c r="E439" s="2">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F439" s="3">
-        <v>45754</v>
+        <v>45755</v>
       </c>
       <c r="G439" s="1" t="s">
         <v>12</v>
@@ -13273,7 +13273,7 @@
         <v>13</v>
       </c>
       <c r="I439" s="4">
-        <v>2413</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="440" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13290,10 +13290,10 @@
         <v>11</v>
       </c>
       <c r="E440" s="2">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="F440" s="3">
-        <v>45755</v>
+        <v>45762</v>
       </c>
       <c r="G440" s="1" t="s">
         <v>12</v>
@@ -13302,7 +13302,7 @@
         <v>13</v>
       </c>
       <c r="I440" s="4">
-        <v>2411</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="441" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13319,10 +13319,10 @@
         <v>11</v>
       </c>
       <c r="E441" s="2">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="F441" s="3">
-        <v>45762</v>
+        <v>45771</v>
       </c>
       <c r="G441" s="1" t="s">
         <v>12</v>
@@ -13348,10 +13348,10 @@
         <v>11</v>
       </c>
       <c r="E442" s="2">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="F442" s="3">
-        <v>45771</v>
+        <v>45775</v>
       </c>
       <c r="G442" s="1" t="s">
         <v>12</v>
@@ -13360,7 +13360,7 @@
         <v>13</v>
       </c>
       <c r="I442" s="4">
-        <v>2407</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="443" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13377,7 +13377,7 @@
         <v>11</v>
       </c>
       <c r="E443" s="2">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="F443" s="3">
         <v>45775</v>
@@ -13389,7 +13389,7 @@
         <v>13</v>
       </c>
       <c r="I443" s="4">
-        <v>2317</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="444" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13406,10 +13406,10 @@
         <v>11</v>
       </c>
       <c r="E444" s="2">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="F444" s="3">
-        <v>45775</v>
+        <v>45776</v>
       </c>
       <c r="G444" s="1" t="s">
         <v>12</v>
@@ -13418,7 +13418,7 @@
         <v>13</v>
       </c>
       <c r="I444" s="4">
-        <v>2503</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="445" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13435,10 +13435,10 @@
         <v>11</v>
       </c>
       <c r="E445" s="2">
-        <v>30</v>
+        <v>320.172414</v>
       </c>
       <c r="F445" s="3">
-        <v>45776</v>
+        <v>45779</v>
       </c>
       <c r="G445" s="1" t="s">
         <v>12</v>
@@ -13447,7 +13447,7 @@
         <v>13</v>
       </c>
       <c r="I445" s="4">
-        <v>2412</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="446" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13464,10 +13464,10 @@
         <v>11</v>
       </c>
       <c r="E446" s="2">
-        <v>320.172414</v>
+        <v>30</v>
       </c>
       <c r="F446" s="3">
-        <v>45779</v>
+        <v>45790</v>
       </c>
       <c r="G446" s="1" t="s">
         <v>12</v>
@@ -13476,7 +13476,7 @@
         <v>13</v>
       </c>
       <c r="I446" s="4">
-        <v>2407</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="447" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13493,10 +13493,10 @@
         <v>11</v>
       </c>
       <c r="E447" s="2">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="F447" s="3">
-        <v>45790</v>
+        <v>45793</v>
       </c>
       <c r="G447" s="1" t="s">
         <v>12</v>
@@ -13505,7 +13505,7 @@
         <v>13</v>
       </c>
       <c r="I447" s="4">
-        <v>2412</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="448" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13522,10 +13522,10 @@
         <v>11</v>
       </c>
       <c r="E448" s="2">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F448" s="3">
-        <v>45793</v>
+        <v>45799</v>
       </c>
       <c r="G448" s="1" t="s">
         <v>12</v>
@@ -13534,7 +13534,7 @@
         <v>13</v>
       </c>
       <c r="I448" s="4">
-        <v>2411</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="449" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13551,10 +13551,10 @@
         <v>11</v>
       </c>
       <c r="E449" s="2">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="F449" s="3">
-        <v>45799</v>
+        <v>45806</v>
       </c>
       <c r="G449" s="1" t="s">
         <v>12</v>
@@ -13563,7 +13563,7 @@
         <v>13</v>
       </c>
       <c r="I449" s="4">
-        <v>2407</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="450" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13574,16 +13574,16 @@
         <v>18</v>
       </c>
       <c r="C450" s="2">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="D450" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E450" s="2">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="F450" s="3">
-        <v>45806</v>
+        <v>45813</v>
       </c>
       <c r="G450" s="1" t="s">
         <v>12</v>
@@ -13592,7 +13592,7 @@
         <v>13</v>
       </c>
       <c r="I450" s="4">
-        <v>2412</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="451" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13609,10 +13609,10 @@
         <v>11</v>
       </c>
       <c r="E451" s="2">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="F451" s="3">
-        <v>45813</v>
+        <v>45819</v>
       </c>
       <c r="G451" s="1" t="s">
         <v>12</v>
@@ -13621,7 +13621,7 @@
         <v>13</v>
       </c>
       <c r="I451" s="4">
-        <v>2317</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="452" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13638,7 +13638,7 @@
         <v>11</v>
       </c>
       <c r="E452" s="2">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="F452" s="3">
         <v>45819</v>
@@ -13650,7 +13650,7 @@
         <v>13</v>
       </c>
       <c r="I452" s="4">
-        <v>2407</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="453" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13667,10 +13667,10 @@
         <v>11</v>
       </c>
       <c r="E453" s="2">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="F453" s="3">
-        <v>45819</v>
+        <v>45821</v>
       </c>
       <c r="G453" s="1" t="s">
         <v>12</v>
@@ -13679,7 +13679,7 @@
         <v>13</v>
       </c>
       <c r="I453" s="4">
-        <v>2412</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="454" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13696,7 +13696,7 @@
         <v>11</v>
       </c>
       <c r="E454" s="2">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="F454" s="3">
         <v>45821</v>
@@ -13708,7 +13708,7 @@
         <v>13</v>
       </c>
       <c r="I454" s="4">
-        <v>2411</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="455" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13725,10 +13725,10 @@
         <v>11</v>
       </c>
       <c r="E455" s="2">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F455" s="3">
-        <v>45821</v>
+        <v>45831</v>
       </c>
       <c r="G455" s="1" t="s">
         <v>12</v>
@@ -13737,7 +13737,7 @@
         <v>13</v>
       </c>
       <c r="I455" s="4">
-        <v>2503</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="456" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13754,10 +13754,10 @@
         <v>11</v>
       </c>
       <c r="E456" s="2">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="F456" s="3">
-        <v>45831</v>
+        <v>45834</v>
       </c>
       <c r="G456" s="1" t="s">
         <v>12</v>
@@ -13766,7 +13766,7 @@
         <v>13</v>
       </c>
       <c r="I456" s="4">
-        <v>2413</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="457" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13783,10 +13783,10 @@
         <v>11</v>
       </c>
       <c r="E457" s="2">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F457" s="3">
-        <v>45834</v>
+        <v>45838</v>
       </c>
       <c r="G457" s="1" t="s">
         <v>12</v>
@@ -13795,7 +13795,7 @@
         <v>13</v>
       </c>
       <c r="I457" s="4">
-        <v>2508</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="458" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13812,10 +13812,10 @@
         <v>11</v>
       </c>
       <c r="E458" s="2">
-        <v>400</v>
+        <v>50</v>
       </c>
       <c r="F458" s="3">
-        <v>45838</v>
+        <v>45840</v>
       </c>
       <c r="G458" s="1" t="s">
         <v>12</v>
@@ -13824,7 +13824,7 @@
         <v>13</v>
       </c>
       <c r="I458" s="4">
-        <v>2317</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="459" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13841,7 +13841,7 @@
         <v>11</v>
       </c>
       <c r="E459" s="2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F459" s="3">
         <v>45840</v>
@@ -13850,10 +13850,10 @@
         <v>12</v>
       </c>
       <c r="H459" s="1" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="I459" s="4">
-        <v>2413</v>
+        <v>9987</v>
       </c>
     </row>
     <row r="460" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13870,7 +13870,7 @@
         <v>11</v>
       </c>
       <c r="E460" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F460" s="3">
         <v>45840</v>
@@ -13899,19 +13899,19 @@
         <v>11</v>
       </c>
       <c r="E461" s="2">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F461" s="3">
-        <v>45840</v>
+        <v>45841</v>
       </c>
       <c r="G461" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H461" s="1" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="I461" s="4">
-        <v>9987</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="462" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13931,7 +13931,7 @@
         <v>50</v>
       </c>
       <c r="F462" s="3">
-        <v>45841</v>
+        <v>45856</v>
       </c>
       <c r="G462" s="1" t="s">
         <v>12</v>
@@ -13940,7 +13940,7 @@
         <v>13</v>
       </c>
       <c r="I462" s="4">
-        <v>2503</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="463" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13957,10 +13957,10 @@
         <v>11</v>
       </c>
       <c r="E463" s="2">
-        <v>50</v>
+        <v>800</v>
       </c>
       <c r="F463" s="3">
-        <v>45856</v>
+        <v>45862</v>
       </c>
       <c r="G463" s="1" t="s">
         <v>12</v>
@@ -13969,7 +13969,7 @@
         <v>13</v>
       </c>
       <c r="I463" s="4">
-        <v>2407</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="464" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13986,10 +13986,10 @@
         <v>11</v>
       </c>
       <c r="E464" s="2">
-        <v>800</v>
+        <v>150</v>
       </c>
       <c r="F464" s="3">
-        <v>45862</v>
+        <v>45869</v>
       </c>
       <c r="G464" s="1" t="s">
         <v>12</v>
@@ -13998,7 +13998,7 @@
         <v>13</v>
       </c>
       <c r="I464" s="4">
-        <v>2317</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="465" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14015,10 +14015,10 @@
         <v>11</v>
       </c>
       <c r="E465" s="2">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="F465" s="3">
-        <v>45869</v>
+        <v>45875</v>
       </c>
       <c r="G465" s="1" t="s">
         <v>12</v>
@@ -14027,7 +14027,7 @@
         <v>13</v>
       </c>
       <c r="I465" s="4">
-        <v>2508</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="466" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14044,10 +14044,10 @@
         <v>11</v>
       </c>
       <c r="E466" s="2">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="F466" s="3">
-        <v>45875</v>
+        <v>45903</v>
       </c>
       <c r="G466" s="1" t="s">
         <v>12</v>
@@ -14073,10 +14073,10 @@
         <v>11</v>
       </c>
       <c r="E467" s="2">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="F467" s="3">
-        <v>45903</v>
+        <v>45911</v>
       </c>
       <c r="G467" s="1" t="s">
         <v>12</v>
@@ -14102,10 +14102,10 @@
         <v>11</v>
       </c>
       <c r="E468" s="2">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="F468" s="3">
-        <v>45911</v>
+        <v>45919</v>
       </c>
       <c r="G468" s="1" t="s">
         <v>12</v>
@@ -14114,7 +14114,7 @@
         <v>13</v>
       </c>
       <c r="I468" s="4">
-        <v>2411</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="469" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14131,10 +14131,10 @@
         <v>11</v>
       </c>
       <c r="E469" s="2">
-        <v>60</v>
+        <v>400</v>
       </c>
       <c r="F469" s="3">
-        <v>45919</v>
+        <v>45924</v>
       </c>
       <c r="G469" s="1" t="s">
         <v>12</v>
@@ -14143,7 +14143,7 @@
         <v>13</v>
       </c>
       <c r="I469" s="4">
-        <v>2512</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="470" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14160,7 +14160,7 @@
         <v>11</v>
       </c>
       <c r="E470" s="2">
-        <v>400</v>
+        <v>32</v>
       </c>
       <c r="F470" s="3">
         <v>45924</v>
@@ -14172,7 +14172,7 @@
         <v>13</v>
       </c>
       <c r="I470" s="4">
-        <v>2317</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="471" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14189,10 +14189,10 @@
         <v>11</v>
       </c>
       <c r="E471" s="2">
-        <v>32</v>
+        <v>700</v>
       </c>
       <c r="F471" s="3">
-        <v>45924</v>
+        <v>45930</v>
       </c>
       <c r="G471" s="1" t="s">
         <v>12</v>
@@ -14201,7 +14201,7 @@
         <v>13</v>
       </c>
       <c r="I471" s="4">
-        <v>2511</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="472" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14218,10 +14218,10 @@
         <v>11</v>
       </c>
       <c r="E472" s="2">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="F472" s="3">
-        <v>45930</v>
+        <v>45938</v>
       </c>
       <c r="G472" s="1" t="s">
         <v>12</v>
@@ -14230,7 +14230,7 @@
         <v>13</v>
       </c>
       <c r="I472" s="4">
-        <v>2411</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="473" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14247,10 +14247,10 @@
         <v>11</v>
       </c>
       <c r="E473" s="2">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F473" s="3">
-        <v>45938</v>
+        <v>45951</v>
       </c>
       <c r="G473" s="1" t="s">
         <v>12</v>
@@ -14259,7 +14259,7 @@
         <v>13</v>
       </c>
       <c r="I473" s="4">
-        <v>2317</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="474" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14279,7 +14279,7 @@
         <v>200</v>
       </c>
       <c r="F474" s="3">
-        <v>45951</v>
+        <v>45957</v>
       </c>
       <c r="G474" s="1" t="s">
         <v>12</v>
@@ -14288,7 +14288,7 @@
         <v>13</v>
       </c>
       <c r="I474" s="4">
-        <v>2411</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="475" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14305,10 +14305,10 @@
         <v>11</v>
       </c>
       <c r="E475" s="2">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F475" s="3">
-        <v>45957</v>
+        <v>45961</v>
       </c>
       <c r="G475" s="1" t="s">
         <v>12</v>
@@ -14317,7 +14317,7 @@
         <v>13</v>
       </c>
       <c r="I475" s="4">
-        <v>2512</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="476" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14334,7 +14334,7 @@
         <v>11</v>
       </c>
       <c r="E476" s="2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F476" s="3">
         <v>45961</v>
@@ -14363,10 +14363,10 @@
         <v>11</v>
       </c>
       <c r="E477" s="2">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F477" s="3">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="G477" s="1" t="s">
         <v>12</v>
@@ -14375,7 +14375,7 @@
         <v>13</v>
       </c>
       <c r="I477" s="4">
-        <v>2511</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="478" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14392,10 +14392,10 @@
         <v>11</v>
       </c>
       <c r="E478" s="2">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F478" s="3">
-        <v>45964</v>
+        <v>45968</v>
       </c>
       <c r="G478" s="1" t="s">
         <v>12</v>
@@ -14404,7 +14404,7 @@
         <v>13</v>
       </c>
       <c r="I478" s="4">
-        <v>2317</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="479" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14421,10 +14421,10 @@
         <v>11</v>
       </c>
       <c r="E479" s="2">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F479" s="3">
-        <v>45968</v>
+        <v>45972</v>
       </c>
       <c r="G479" s="1" t="s">
         <v>12</v>
@@ -14433,7 +14433,7 @@
         <v>13</v>
       </c>
       <c r="I479" s="4">
-        <v>2511</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="480" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14450,10 +14450,10 @@
         <v>11</v>
       </c>
       <c r="E480" s="2">
-        <v>250</v>
+        <v>800</v>
       </c>
       <c r="F480" s="3">
-        <v>45972</v>
+        <v>45978</v>
       </c>
       <c r="G480" s="1" t="s">
         <v>12</v>
@@ -14462,7 +14462,7 @@
         <v>13</v>
       </c>
       <c r="I480" s="4">
-        <v>2411</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="481" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14479,10 +14479,10 @@
         <v>11</v>
       </c>
       <c r="E481" s="2">
-        <v>800</v>
+        <v>50</v>
       </c>
       <c r="F481" s="3">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="G481" s="1" t="s">
         <v>12</v>
@@ -14491,7 +14491,7 @@
         <v>13</v>
       </c>
       <c r="I481" s="4">
-        <v>2317</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="482" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14508,10 +14508,10 @@
         <v>11</v>
       </c>
       <c r="E482" s="2">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F482" s="3">
-        <v>45979</v>
+        <v>45981</v>
       </c>
       <c r="G482" s="1" t="s">
         <v>12</v>
@@ -14520,7 +14520,7 @@
         <v>13</v>
       </c>
       <c r="I482" s="4">
-        <v>2512</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="483" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14537,10 +14537,10 @@
         <v>11</v>
       </c>
       <c r="E483" s="2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F483" s="3">
-        <v>45981</v>
+        <v>45988</v>
       </c>
       <c r="G483" s="1" t="s">
         <v>12</v>
@@ -14549,7 +14549,7 @@
         <v>13</v>
       </c>
       <c r="I483" s="4">
-        <v>2516</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="484" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14578,7 +14578,7 @@
         <v>13</v>
       </c>
       <c r="I484" s="4">
-        <v>2511</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="485" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14595,10 +14595,10 @@
         <v>11</v>
       </c>
       <c r="E485" s="2">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F485" s="3">
-        <v>45988</v>
+        <v>45995</v>
       </c>
       <c r="G485" s="1" t="s">
         <v>12</v>
@@ -14607,7 +14607,7 @@
         <v>13</v>
       </c>
       <c r="I485" s="4">
-        <v>2512</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="486" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14624,10 +14624,10 @@
         <v>11</v>
       </c>
       <c r="E486" s="2">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F486" s="3">
-        <v>45995</v>
+        <v>46001</v>
       </c>
       <c r="G486" s="1" t="s">
         <v>12</v>
@@ -14636,7 +14636,7 @@
         <v>13</v>
       </c>
       <c r="I486" s="4">
-        <v>2511</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="487" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14653,10 +14653,10 @@
         <v>11</v>
       </c>
       <c r="E487" s="2">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F487" s="3">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="G487" s="1" t="s">
         <v>12</v>
@@ -14665,7 +14665,7 @@
         <v>13</v>
       </c>
       <c r="I487" s="4">
-        <v>2512</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="488" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14682,7 +14682,7 @@
         <v>11</v>
       </c>
       <c r="E488" s="2">
-        <v>20</v>
+        <v>1500</v>
       </c>
       <c r="F488" s="3">
         <v>46002</v>
@@ -14694,7 +14694,7 @@
         <v>13</v>
       </c>
       <c r="I488" s="4">
-        <v>2411</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="489" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14711,10 +14711,10 @@
         <v>11</v>
       </c>
       <c r="E489" s="2">
-        <v>1500</v>
+        <v>400</v>
       </c>
       <c r="F489" s="3">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="G489" s="1" t="s">
         <v>12</v>
@@ -14723,7 +14723,7 @@
         <v>13</v>
       </c>
       <c r="I489" s="4">
-        <v>2511</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="490" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14743,7 +14743,7 @@
         <v>400</v>
       </c>
       <c r="F490" s="3">
-        <v>46006</v>
+        <v>46013</v>
       </c>
       <c r="G490" s="1" t="s">
         <v>12</v>
@@ -14769,10 +14769,10 @@
         <v>11</v>
       </c>
       <c r="E491" s="2">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F491" s="3">
-        <v>46013</v>
+        <v>46029</v>
       </c>
       <c r="G491" s="1" t="s">
         <v>12</v>
@@ -14798,10 +14798,10 @@
         <v>11</v>
       </c>
       <c r="E492" s="2">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="F492" s="3">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="G492" s="1" t="s">
         <v>12</v>
@@ -14810,7 +14810,7 @@
         <v>13</v>
       </c>
       <c r="I492" s="4">
-        <v>2317</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="493" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14827,10 +14827,10 @@
         <v>11</v>
       </c>
       <c r="E493" s="2">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="F493" s="3">
-        <v>46030</v>
+        <v>46044</v>
       </c>
       <c r="G493" s="1" t="s">
         <v>12</v>
@@ -14839,7 +14839,7 @@
         <v>13</v>
       </c>
       <c r="I493" s="4">
-        <v>2411</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="494" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14859,7 +14859,7 @@
         <v>300</v>
       </c>
       <c r="F494" s="3">
-        <v>46044</v>
+        <v>46049</v>
       </c>
       <c r="G494" s="1" t="s">
         <v>12</v>
@@ -14868,7 +14868,7 @@
         <v>13</v>
       </c>
       <c r="I494" s="4">
-        <v>2317</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="495" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14888,7 +14888,7 @@
         <v>300</v>
       </c>
       <c r="F495" s="3">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="G495" s="1" t="s">
         <v>12</v>
@@ -14897,7 +14897,7 @@
         <v>13</v>
       </c>
       <c r="I495" s="4">
-        <v>2516</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="496" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14917,7 +14917,7 @@
         <v>300</v>
       </c>
       <c r="F496" s="3">
-        <v>46050</v>
+        <v>46055</v>
       </c>
       <c r="G496" s="1" t="s">
         <v>12</v>
@@ -14926,7 +14926,7 @@
         <v>13</v>
       </c>
       <c r="I496" s="4">
-        <v>2317</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="497" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14943,10 +14943,10 @@
         <v>11</v>
       </c>
       <c r="E497" s="2">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F497" s="3">
-        <v>46055</v>
+        <v>46058</v>
       </c>
       <c r="G497" s="1" t="s">
         <v>12</v>
@@ -14955,7 +14955,7 @@
         <v>13</v>
       </c>
       <c r="I497" s="4">
-        <v>2516</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="498" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14972,10 +14972,10 @@
         <v>11</v>
       </c>
       <c r="E498" s="2">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F498" s="3">
-        <v>46058</v>
+        <v>46065</v>
       </c>
       <c r="G498" s="1" t="s">
         <v>12</v>
@@ -14984,7 +14984,7 @@
         <v>13</v>
       </c>
       <c r="I498" s="4">
-        <v>2317</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="499" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15001,10 +15001,10 @@
         <v>11</v>
       </c>
       <c r="E499" s="2">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="F499" s="3">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="G499" s="1" t="s">
         <v>12</v>
@@ -15013,7 +15013,7 @@
         <v>13</v>
       </c>
       <c r="I499" s="4">
-        <v>2516</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="500" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15030,10 +15030,10 @@
         <v>11</v>
       </c>
       <c r="E500" s="2">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="F500" s="3">
-        <v>46066</v>
+        <v>46076</v>
       </c>
       <c r="G500" s="1" t="s">
         <v>12</v>
@@ -15059,7 +15059,7 @@
         <v>11</v>
       </c>
       <c r="E501" s="2">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="F501" s="3">
         <v>46076</v>
@@ -15071,7 +15071,7 @@
         <v>13</v>
       </c>
       <c r="I501" s="4">
-        <v>2317</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="502" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15088,10 +15088,10 @@
         <v>11</v>
       </c>
       <c r="E502" s="2">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="F502" s="3">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="G502" s="1" t="s">
         <v>12</v>
@@ -15100,7 +15100,7 @@
         <v>13</v>
       </c>
       <c r="I502" s="4">
-        <v>2512</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="503" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15120,7 +15120,7 @@
         <v>200</v>
       </c>
       <c r="F503" s="3">
-        <v>46077</v>
+        <v>46083</v>
       </c>
       <c r="G503" s="1" t="s">
         <v>12</v>
@@ -15146,10 +15146,10 @@
         <v>11</v>
       </c>
       <c r="E504" s="2">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F504" s="3">
-        <v>46083</v>
+        <v>46099</v>
       </c>
       <c r="G504" s="1" t="s">
         <v>12</v>
@@ -15158,7 +15158,7 @@
         <v>13</v>
       </c>
       <c r="I504" s="4">
-        <v>2516</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="505" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15175,10 +15175,10 @@
         <v>11</v>
       </c>
       <c r="E505" s="2">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="F505" s="3">
-        <v>46099</v>
+        <v>46106</v>
       </c>
       <c r="G505" s="1" t="s">
         <v>12</v>
@@ -15187,7 +15187,7 @@
         <v>13</v>
       </c>
       <c r="I505" s="4">
-        <v>2511</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="506" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15204,10 +15204,10 @@
         <v>11</v>
       </c>
       <c r="E506" s="2">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="F506" s="3">
-        <v>46106</v>
+        <v>46118</v>
       </c>
       <c r="G506" s="1" t="s">
         <v>12</v>
@@ -15216,7 +15216,7 @@
         <v>13</v>
       </c>
       <c r="I506" s="4">
-        <v>2317</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="507" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15236,7 +15236,7 @@
         <v>100</v>
       </c>
       <c r="F507" s="3">
-        <v>46118</v>
+        <v>46134</v>
       </c>
       <c r="G507" s="1" t="s">
         <v>12</v>
@@ -15262,10 +15262,10 @@
         <v>11</v>
       </c>
       <c r="E508" s="2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F508" s="3">
-        <v>46134</v>
+        <v>46142</v>
       </c>
       <c r="G508" s="1" t="s">
         <v>12</v>
@@ -15274,7 +15274,7 @@
         <v>13</v>
       </c>
       <c r="I508" s="4">
-        <v>2516</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="509" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15294,16 +15294,16 @@
         <v>200</v>
       </c>
       <c r="F509" s="3">
-        <v>46142</v>
+        <v>46153</v>
       </c>
       <c r="G509" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H509" s="1" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="I509" s="4">
-        <v>2601</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="510" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15320,7 +15320,7 @@
         <v>11</v>
       </c>
       <c r="E510" s="2">
-        <v>200</v>
+        <v>15</v>
       </c>
       <c r="F510" s="3">
         <v>46153</v>
@@ -15329,10 +15329,10 @@
         <v>12</v>
       </c>
       <c r="H510" s="1" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="I510" s="4">
-        <v>2516</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="511" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15349,10 +15349,10 @@
         <v>11</v>
       </c>
       <c r="E511" s="2">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="F511" s="3">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="G511" s="1" t="s">
         <v>12</v>
@@ -15361,7 +15361,7 @@
         <v>13</v>
       </c>
       <c r="I511" s="4">
-        <v>2606</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="512" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15378,10 +15378,10 @@
         <v>11</v>
       </c>
       <c r="E512" s="2">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="F512" s="3">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="G512" s="1" t="s">
         <v>12</v>
@@ -15390,7 +15390,7 @@
         <v>13</v>
       </c>
       <c r="I512" s="4">
-        <v>2211</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="513" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15407,10 +15407,10 @@
         <v>11</v>
       </c>
       <c r="E513" s="2">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F513" s="3">
-        <v>46157</v>
+        <v>46171</v>
       </c>
       <c r="G513" s="1" t="s">
         <v>12</v>
@@ -15419,7 +15419,7 @@
         <v>13</v>
       </c>
       <c r="I513" s="4">
-        <v>2512</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="514" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15436,19 +15436,19 @@
         <v>11</v>
       </c>
       <c r="E514" s="2">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F514" s="3">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="G514" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H514" s="1" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="I514" s="4">
-        <v>2606</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="515" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15465,7 +15465,7 @@
         <v>11</v>
       </c>
       <c r="E515" s="2">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F515" s="3">
         <v>46174</v>
@@ -15477,7 +15477,7 @@
         <v>46</v>
       </c>
       <c r="I515" s="4">
-        <v>2516</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="516" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15494,7 +15494,7 @@
         <v>11</v>
       </c>
       <c r="E516" s="2">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="F516" s="3">
         <v>46174</v>
@@ -15503,7 +15503,7 @@
         <v>12</v>
       </c>
       <c r="H516" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I516" s="4">
         <v>2601</v>
@@ -15526,16 +15526,16 @@
         <v>300</v>
       </c>
       <c r="F517" s="3">
-        <v>46174</v>
+        <v>46183</v>
       </c>
       <c r="G517" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H517" s="1" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="I517" s="4">
-        <v>2601</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="518" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15552,10 +15552,10 @@
         <v>11</v>
       </c>
       <c r="E518" s="2">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="F518" s="3">
-        <v>46183</v>
+        <v>46188</v>
       </c>
       <c r="G518" s="1" t="s">
         <v>12</v>
@@ -15564,7 +15564,7 @@
         <v>13</v>
       </c>
       <c r="I518" s="4">
-        <v>2606</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="519" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15581,10 +15581,10 @@
         <v>11</v>
       </c>
       <c r="E519" s="2">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="F519" s="3">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="G519" s="1" t="s">
         <v>12</v>
@@ -15593,7 +15593,7 @@
         <v>13</v>
       </c>
       <c r="I519" s="4">
-        <v>2601</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="520" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15610,10 +15610,10 @@
         <v>11</v>
       </c>
       <c r="E520" s="2">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="F520" s="3">
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="G520" s="1" t="s">
         <v>12</v>
@@ -15622,7 +15622,7 @@
         <v>13</v>
       </c>
       <c r="I520" s="4">
-        <v>2605</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="521" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15639,10 +15639,10 @@
         <v>11</v>
       </c>
       <c r="E521" s="2">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="F521" s="3">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="G521" s="1" t="s">
         <v>12</v>
@@ -15651,7 +15651,7 @@
         <v>13</v>
       </c>
       <c r="I521" s="4">
-        <v>2606</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="522" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15668,10 +15668,10 @@
         <v>11</v>
       </c>
       <c r="E522" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F522" s="3">
-        <v>46197</v>
+        <v>46211</v>
       </c>
       <c r="G522" s="1" t="s">
         <v>12</v>
@@ -15680,7 +15680,7 @@
         <v>13</v>
       </c>
       <c r="I522" s="4">
-        <v>2602</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="523" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15697,10 +15697,10 @@
         <v>11</v>
       </c>
       <c r="E523" s="2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F523" s="3">
-        <v>46211</v>
+        <v>46224</v>
       </c>
       <c r="G523" s="1" t="s">
         <v>12</v>
@@ -15709,7 +15709,7 @@
         <v>13</v>
       </c>
       <c r="I523" s="4">
-        <v>2605</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="524" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15726,10 +15726,10 @@
         <v>11</v>
       </c>
       <c r="E524" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F524" s="3">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="G524" s="1" t="s">
         <v>12</v>
@@ -15738,7 +15738,7 @@
         <v>13</v>
       </c>
       <c r="I524" s="4">
-        <v>2602</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="525" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15755,19 +15755,19 @@
         <v>11</v>
       </c>
       <c r="E525" s="2">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="F525" s="3">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="G525" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H525" s="1" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="I525" s="4">
-        <v>2605</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="526" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15784,19 +15784,19 @@
         <v>11</v>
       </c>
       <c r="E526" s="2">
-        <v>600</v>
+        <v>120</v>
       </c>
       <c r="F526" s="3">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="G526" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H526" s="1" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="I526" s="4">
-        <v>2606</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="527" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15813,10 +15813,10 @@
         <v>11</v>
       </c>
       <c r="E527" s="2">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="F527" s="3">
-        <v>46231</v>
+        <v>46234</v>
       </c>
       <c r="G527" s="1" t="s">
         <v>12</v>
@@ -15825,7 +15825,7 @@
         <v>13</v>
       </c>
       <c r="I527" s="4">
-        <v>2317</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="528" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15842,7 +15842,7 @@
         <v>11</v>
       </c>
       <c r="E528" s="2">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="F528" s="3">
         <v>46234</v>
@@ -15871,7 +15871,7 @@
         <v>11</v>
       </c>
       <c r="E529" s="2">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="F529" s="3">
         <v>46234</v>
@@ -15883,7 +15883,7 @@
         <v>13</v>
       </c>
       <c r="I529" s="4">
-        <v>2601</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="530" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15900,19 +15900,19 @@
         <v>11</v>
       </c>
       <c r="E530" s="2">
-        <v>50</v>
+        <v>600</v>
       </c>
       <c r="F530" s="3">
-        <v>46234</v>
+        <v>46239</v>
       </c>
       <c r="G530" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H530" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I530" s="4">
-        <v>2602</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="531" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15932,13 +15932,13 @@
         <v>600</v>
       </c>
       <c r="F531" s="3">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="G531" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H531" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I531" s="4">
         <v>2606</v>
@@ -15958,19 +15958,19 @@
         <v>11</v>
       </c>
       <c r="E532" s="2">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="F532" s="3">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="G532" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H532" s="1" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="I532" s="4">
-        <v>2606</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="533" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15987,19 +15987,19 @@
         <v>11</v>
       </c>
       <c r="E533" s="2">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F533" s="3">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="G533" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H533" s="1" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="I533" s="4">
-        <v>2601</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="534" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16019,16 +16019,16 @@
         <v>100</v>
       </c>
       <c r="F534" s="3">
-        <v>46248</v>
+        <v>46254</v>
       </c>
       <c r="G534" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H534" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I534" s="4">
-        <v>2605</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="535" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16045,7 +16045,7 @@
         <v>11</v>
       </c>
       <c r="E535" s="2">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F535" s="3">
         <v>46254</v>
@@ -16057,7 +16057,7 @@
         <v>16</v>
       </c>
       <c r="I535" s="4">
-        <v>2601</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="536" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16074,10 +16074,10 @@
         <v>11</v>
       </c>
       <c r="E536" s="2">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F536" s="3">
-        <v>46254</v>
+        <v>46259</v>
       </c>
       <c r="G536" s="1" t="s">
         <v>12</v>
@@ -16086,7 +16086,7 @@
         <v>16</v>
       </c>
       <c r="I536" s="4">
-        <v>2607</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="537" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16103,19 +16103,19 @@
         <v>11</v>
       </c>
       <c r="E537" s="2">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F537" s="3">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="G537" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H537" s="1" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="I537" s="4">
-        <v>2605</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="538" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16132,19 +16132,19 @@
         <v>11</v>
       </c>
       <c r="E538" s="2">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="F538" s="3">
-        <v>46261</v>
+        <v>46273</v>
       </c>
       <c r="G538" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H538" s="1" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="I538" s="4">
-        <v>2602</v>
+        <v>2611</v>
       </c>
     </row>
     <row r="539" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16161,10 +16161,10 @@
         <v>11</v>
       </c>
       <c r="E539" s="2">
-        <v>1000</v>
+        <v>711</v>
       </c>
       <c r="F539" s="3">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G539" s="1" t="s">
         <v>12</v>
@@ -16173,7 +16173,7 @@
         <v>16</v>
       </c>
       <c r="I539" s="4">
-        <v>2611</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="540" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16190,10 +16190,10 @@
         <v>11</v>
       </c>
       <c r="E540" s="2">
-        <v>711</v>
+        <v>300</v>
       </c>
       <c r="F540" s="3">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="G540" s="1" t="s">
         <v>12</v>
@@ -16202,7 +16202,7 @@
         <v>16</v>
       </c>
       <c r="I540" s="4">
-        <v>2605</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="541" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16219,10 +16219,10 @@
         <v>11</v>
       </c>
       <c r="E541" s="2">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F541" s="3">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="G541" s="1" t="s">
         <v>12</v>
@@ -16231,7 +16231,7 @@
         <v>16</v>
       </c>
       <c r="I541" s="4">
-        <v>2607</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="542" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16248,7 +16248,7 @@
         <v>11</v>
       </c>
       <c r="E542" s="2">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="F542" s="3">
         <v>46276</v>
@@ -16257,10 +16257,10 @@
         <v>12</v>
       </c>
       <c r="H542" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I542" s="4">
-        <v>2601</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="543" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16277,19 +16277,19 @@
         <v>11</v>
       </c>
       <c r="E543" s="2">
-        <v>15</v>
+        <v>700</v>
       </c>
       <c r="F543" s="3">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="G543" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H543" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I543" s="4">
-        <v>2612</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="544" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16306,10 +16306,10 @@
         <v>11</v>
       </c>
       <c r="E544" s="2">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="F544" s="3">
-        <v>46283</v>
+        <v>46287</v>
       </c>
       <c r="G544" s="1" t="s">
         <v>12</v>
@@ -16318,7 +16318,7 @@
         <v>16</v>
       </c>
       <c r="I544" s="4">
-        <v>2601</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="545" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16338,7 +16338,7 @@
         <v>200</v>
       </c>
       <c r="F545" s="3">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="G545" s="1" t="s">
         <v>12</v>
@@ -16347,7 +16347,7 @@
         <v>16</v>
       </c>
       <c r="I545" s="4">
-        <v>2607</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="546" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16364,10 +16364,10 @@
         <v>11</v>
       </c>
       <c r="E546" s="2">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F546" s="3">
-        <v>46289</v>
+        <v>46297</v>
       </c>
       <c r="G546" s="1" t="s">
         <v>12</v>
@@ -16376,36 +16376,36 @@
         <v>16</v>
       </c>
       <c r="I546" s="4">
-        <v>2612</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="547" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B547" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C547" s="2">
-        <v>5.8</v>
+        <v>32.9</v>
       </c>
       <c r="D547" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E547" s="2">
-        <v>400</v>
+        <v>10</v>
       </c>
       <c r="F547" s="3">
-        <v>46297</v>
+        <v>45660</v>
       </c>
       <c r="G547" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H547" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I547" s="4">
-        <v>2605</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="548" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16422,10 +16422,10 @@
         <v>11</v>
       </c>
       <c r="E548" s="2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F548" s="3">
-        <v>45660</v>
+        <v>45671</v>
       </c>
       <c r="G548" s="1" t="s">
         <v>12</v>
@@ -16434,7 +16434,7 @@
         <v>13</v>
       </c>
       <c r="I548" s="4">
-        <v>2413</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="549" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16445,13 +16445,13 @@
         <v>20</v>
       </c>
       <c r="C549" s="2">
-        <v>32.9</v>
+        <v>43</v>
       </c>
       <c r="D549" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E549" s="2">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="F549" s="3">
         <v>45671</v>
@@ -16460,10 +16460,10 @@
         <v>12</v>
       </c>
       <c r="H549" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="I549" s="4">
-        <v>2306</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="550" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16474,25 +16474,25 @@
         <v>20</v>
       </c>
       <c r="C550" s="2">
-        <v>43</v>
+        <v>32.9</v>
       </c>
       <c r="D550" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E550" s="2">
-        <v>40</v>
+        <v>99.978723000000002</v>
       </c>
       <c r="F550" s="3">
-        <v>45671</v>
+        <v>45672</v>
       </c>
       <c r="G550" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H550" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="I550" s="4">
-        <v>2310</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="551" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16503,25 +16503,25 @@
         <v>20</v>
       </c>
       <c r="C551" s="2">
-        <v>32.9</v>
+        <v>29.5</v>
       </c>
       <c r="D551" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E551" s="2">
-        <v>99.978723000000002</v>
+        <v>50</v>
       </c>
       <c r="F551" s="3">
-        <v>45672</v>
+        <v>45674</v>
       </c>
       <c r="G551" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H551" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I551" s="4">
-        <v>2407</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="552" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16532,16 +16532,16 @@
         <v>20</v>
       </c>
       <c r="C552" s="2">
-        <v>29.5</v>
+        <v>31.58</v>
       </c>
       <c r="D552" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E552" s="2">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F552" s="3">
-        <v>45674</v>
+        <v>45678</v>
       </c>
       <c r="G552" s="1" t="s">
         <v>12</v>
@@ -16550,7 +16550,7 @@
         <v>16</v>
       </c>
       <c r="I552" s="4">
-        <v>2411</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="553" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16561,7 +16561,7 @@
         <v>20</v>
       </c>
       <c r="C553" s="2">
-        <v>31.58</v>
+        <v>42</v>
       </c>
       <c r="D553" s="1" t="s">
         <v>11</v>
@@ -16570,16 +16570,16 @@
         <v>10</v>
       </c>
       <c r="F553" s="3">
-        <v>45678</v>
+        <v>45684</v>
       </c>
       <c r="G553" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H553" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I553" s="4">
-        <v>2412</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="554" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16590,25 +16590,25 @@
         <v>20</v>
       </c>
       <c r="C554" s="2">
-        <v>42</v>
+        <v>32.9</v>
       </c>
       <c r="D554" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E554" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F554" s="3">
-        <v>45684</v>
+        <v>45686</v>
       </c>
       <c r="G554" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H554" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="I554" s="4">
-        <v>2310</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="555" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16619,25 +16619,25 @@
         <v>20</v>
       </c>
       <c r="C555" s="2">
-        <v>32.9</v>
+        <v>35</v>
       </c>
       <c r="D555" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E555" s="2">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="F555" s="3">
-        <v>45686</v>
+        <v>45693</v>
       </c>
       <c r="G555" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H555" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="I555" s="4">
-        <v>2413</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="556" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16648,25 +16648,25 @@
         <v>20</v>
       </c>
       <c r="C556" s="2">
-        <v>35</v>
+        <v>31.883099999999999</v>
       </c>
       <c r="D556" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E556" s="2">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F556" s="3">
-        <v>45693</v>
+        <v>45694</v>
       </c>
       <c r="G556" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H556" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I556" s="4">
-        <v>2502</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="557" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16677,16 +16677,16 @@
         <v>20</v>
       </c>
       <c r="C557" s="2">
-        <v>31.883099999999999</v>
+        <v>29.5</v>
       </c>
       <c r="D557" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E557" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F557" s="3">
-        <v>45694</v>
+        <v>45695</v>
       </c>
       <c r="G557" s="1" t="s">
         <v>12</v>
@@ -16695,7 +16695,7 @@
         <v>16</v>
       </c>
       <c r="I557" s="4">
-        <v>2411</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="558" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16706,25 +16706,25 @@
         <v>20</v>
       </c>
       <c r="C558" s="2">
-        <v>29.5</v>
+        <v>32.9</v>
       </c>
       <c r="D558" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E558" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F558" s="3">
-        <v>45695</v>
+        <v>45699</v>
       </c>
       <c r="G558" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H558" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I558" s="4">
-        <v>2413</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="559" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16735,13 +16735,13 @@
         <v>20</v>
       </c>
       <c r="C559" s="2">
-        <v>32.9</v>
+        <v>29.5</v>
       </c>
       <c r="D559" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E559" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F559" s="3">
         <v>45699</v>
@@ -16750,10 +16750,10 @@
         <v>12</v>
       </c>
       <c r="H559" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I559" s="4">
-        <v>2412</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="560" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16764,7 +16764,7 @@
         <v>20</v>
       </c>
       <c r="C560" s="2">
-        <v>29.5</v>
+        <v>35.9</v>
       </c>
       <c r="D560" s="1" t="s">
         <v>11</v>
@@ -16773,16 +16773,16 @@
         <v>20</v>
       </c>
       <c r="F560" s="3">
-        <v>45699</v>
+        <v>45701</v>
       </c>
       <c r="G560" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H560" s="1" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="I560" s="4">
-        <v>2503</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="561" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16793,25 +16793,25 @@
         <v>20</v>
       </c>
       <c r="C561" s="2">
-        <v>35.9</v>
+        <v>29.6</v>
       </c>
       <c r="D561" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E561" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F561" s="3">
-        <v>45701</v>
+        <v>45702</v>
       </c>
       <c r="G561" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H561" s="1" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I561" s="4">
-        <v>2502</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="562" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16822,7 +16822,7 @@
         <v>20</v>
       </c>
       <c r="C562" s="2">
-        <v>29.6</v>
+        <v>29.9</v>
       </c>
       <c r="D562" s="1" t="s">
         <v>11</v>
@@ -16831,7 +16831,7 @@
         <v>100</v>
       </c>
       <c r="F562" s="3">
-        <v>45702</v>
+        <v>45706</v>
       </c>
       <c r="G562" s="1" t="s">
         <v>12</v>
@@ -16840,7 +16840,7 @@
         <v>16</v>
       </c>
       <c r="I562" s="4">
-        <v>2317</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="563" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16851,13 +16851,13 @@
         <v>20</v>
       </c>
       <c r="C563" s="2">
-        <v>29.9</v>
+        <v>35.39</v>
       </c>
       <c r="D563" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E563" s="2">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="F563" s="3">
         <v>45706</v>
@@ -16866,10 +16866,10 @@
         <v>12</v>
       </c>
       <c r="H563" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I563" s="4">
-        <v>2411</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="564" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16880,13 +16880,13 @@
         <v>20</v>
       </c>
       <c r="C564" s="2">
-        <v>35.39</v>
+        <v>32.9</v>
       </c>
       <c r="D564" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E564" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F564" s="3">
         <v>45706</v>
@@ -16895,10 +16895,10 @@
         <v>12</v>
       </c>
       <c r="H564" s="1" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="I564" s="4">
-        <v>2413</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="565" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16909,25 +16909,25 @@
         <v>20</v>
       </c>
       <c r="C565" s="2">
-        <v>32.9</v>
+        <v>29.8</v>
       </c>
       <c r="D565" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E565" s="2">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="F565" s="3">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G565" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H565" s="1" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I565" s="4">
-        <v>2502</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="566" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16944,10 +16944,10 @@
         <v>11</v>
       </c>
       <c r="E566" s="2">
-        <v>200</v>
+        <v>49.995429999999999</v>
       </c>
       <c r="F566" s="3">
-        <v>45709</v>
+        <v>45711</v>
       </c>
       <c r="G566" s="1" t="s">
         <v>12</v>
@@ -16956,7 +16956,7 @@
         <v>16</v>
       </c>
       <c r="I566" s="4">
-        <v>2411</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="567" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16967,16 +16967,16 @@
         <v>20</v>
       </c>
       <c r="C567" s="2">
-        <v>29.8</v>
+        <v>29.5</v>
       </c>
       <c r="D567" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E567" s="2">
-        <v>49.995429999999999</v>
+        <v>96.393217000000007</v>
       </c>
       <c r="F567" s="3">
-        <v>45711</v>
+        <v>45722</v>
       </c>
       <c r="G567" s="1" t="s">
         <v>12</v>
@@ -16996,16 +16996,16 @@
         <v>20</v>
       </c>
       <c r="C568" s="2">
-        <v>29.5</v>
+        <v>33.6</v>
       </c>
       <c r="D568" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E568" s="2">
-        <v>96.393217000000007</v>
+        <v>40</v>
       </c>
       <c r="F568" s="3">
-        <v>45722</v>
+        <v>45730</v>
       </c>
       <c r="G568" s="1" t="s">
         <v>12</v>
@@ -17014,7 +17014,7 @@
         <v>16</v>
       </c>
       <c r="I568" s="4">
-        <v>2407</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="569" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17025,16 +17025,16 @@
         <v>20</v>
       </c>
       <c r="C569" s="2">
-        <v>33.6</v>
+        <v>36.9</v>
       </c>
       <c r="D569" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E569" s="2">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="F569" s="3">
-        <v>45730</v>
+        <v>45736</v>
       </c>
       <c r="G569" s="1" t="s">
         <v>12</v>
@@ -17043,7 +17043,7 @@
         <v>16</v>
       </c>
       <c r="I569" s="4">
-        <v>2413</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="570" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17060,10 +17060,10 @@
         <v>11</v>
       </c>
       <c r="E570" s="2">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="F570" s="3">
-        <v>45736</v>
+        <v>45737</v>
       </c>
       <c r="G570" s="1" t="s">
         <v>12</v>
@@ -17072,7 +17072,7 @@
         <v>16</v>
       </c>
       <c r="I570" s="4">
-        <v>2411</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="571" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17083,13 +17083,13 @@
         <v>20</v>
       </c>
       <c r="C571" s="2">
-        <v>36.9</v>
+        <v>34.9</v>
       </c>
       <c r="D571" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E571" s="2">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F571" s="3">
         <v>45737</v>
@@ -17098,10 +17098,10 @@
         <v>12</v>
       </c>
       <c r="H571" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I571" s="4">
-        <v>2412</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="572" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17112,7 +17112,7 @@
         <v>20</v>
       </c>
       <c r="C572" s="2">
-        <v>34.9</v>
+        <v>33.9</v>
       </c>
       <c r="D572" s="1" t="s">
         <v>11</v>
@@ -17121,7 +17121,7 @@
         <v>20</v>
       </c>
       <c r="F572" s="3">
-        <v>45737</v>
+        <v>45743</v>
       </c>
       <c r="G572" s="1" t="s">
         <v>12</v>
@@ -17147,10 +17147,10 @@
         <v>11</v>
       </c>
       <c r="E573" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F573" s="3">
-        <v>45743</v>
+        <v>45747</v>
       </c>
       <c r="G573" s="1" t="s">
         <v>12</v>
@@ -17159,7 +17159,7 @@
         <v>13</v>
       </c>
       <c r="I573" s="4">
-        <v>2503</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="574" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17170,16 +17170,16 @@
         <v>20</v>
       </c>
       <c r="C574" s="2">
-        <v>33.9</v>
+        <v>34.9</v>
       </c>
       <c r="D574" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E574" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F574" s="3">
-        <v>45747</v>
+        <v>45751</v>
       </c>
       <c r="G574" s="1" t="s">
         <v>12</v>
@@ -17188,7 +17188,7 @@
         <v>13</v>
       </c>
       <c r="I574" s="4">
-        <v>2412</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="575" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17205,10 +17205,10 @@
         <v>11</v>
       </c>
       <c r="E575" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F575" s="3">
-        <v>45751</v>
+        <v>45775</v>
       </c>
       <c r="G575" s="1" t="s">
         <v>12</v>
@@ -17234,10 +17234,10 @@
         <v>11</v>
       </c>
       <c r="E576" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F576" s="3">
-        <v>45775</v>
+        <v>45776</v>
       </c>
       <c r="G576" s="1" t="s">
         <v>12</v>
@@ -17246,7 +17246,7 @@
         <v>13</v>
       </c>
       <c r="I576" s="4">
-        <v>2503</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="577" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17263,10 +17263,10 @@
         <v>11</v>
       </c>
       <c r="E577" s="2">
-        <v>4</v>
+        <v>76.633238000000006</v>
       </c>
       <c r="F577" s="3">
-        <v>45776</v>
+        <v>45779</v>
       </c>
       <c r="G577" s="1" t="s">
         <v>12</v>
@@ -17275,7 +17275,7 @@
         <v>13</v>
       </c>
       <c r="I577" s="4">
-        <v>2412</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="578" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17292,7 +17292,7 @@
         <v>11</v>
       </c>
       <c r="E578" s="2">
-        <v>76.633238000000006</v>
+        <v>10</v>
       </c>
       <c r="F578" s="3">
         <v>45779</v>
@@ -17304,7 +17304,7 @@
         <v>13</v>
       </c>
       <c r="I578" s="4">
-        <v>2407</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="579" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17321,10 +17321,10 @@
         <v>11</v>
       </c>
       <c r="E579" s="2">
-        <v>10</v>
+        <v>0.27507199999999998</v>
       </c>
       <c r="F579" s="3">
-        <v>45779</v>
+        <v>45790</v>
       </c>
       <c r="G579" s="1" t="s">
         <v>12</v>
@@ -17333,7 +17333,7 @@
         <v>13</v>
       </c>
       <c r="I579" s="4">
-        <v>2503</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="580" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17350,10 +17350,10 @@
         <v>11</v>
       </c>
       <c r="E580" s="2">
-        <v>0.27507199999999998</v>
+        <v>50</v>
       </c>
       <c r="F580" s="3">
-        <v>45790</v>
+        <v>45799</v>
       </c>
       <c r="G580" s="1" t="s">
         <v>12</v>
@@ -17362,7 +17362,7 @@
         <v>13</v>
       </c>
       <c r="I580" s="4">
-        <v>2412</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="581" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17379,10 +17379,10 @@
         <v>11</v>
       </c>
       <c r="E581" s="2">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F581" s="3">
-        <v>45799</v>
+        <v>45803</v>
       </c>
       <c r="G581" s="1" t="s">
         <v>12</v>
@@ -17391,7 +17391,7 @@
         <v>13</v>
       </c>
       <c r="I581" s="4">
-        <v>2407</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="582" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17408,10 +17408,10 @@
         <v>11</v>
       </c>
       <c r="E582" s="2">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F582" s="3">
-        <v>45803</v>
+        <v>45806</v>
       </c>
       <c r="G582" s="1" t="s">
         <v>12</v>
@@ -17420,7 +17420,7 @@
         <v>13</v>
       </c>
       <c r="I582" s="4">
-        <v>2413</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="583" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17431,13 +17431,13 @@
         <v>20</v>
       </c>
       <c r="C583" s="2">
-        <v>34.9</v>
+        <v>34.5</v>
       </c>
       <c r="D583" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E583" s="2">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F583" s="3">
         <v>45806</v>
@@ -17449,7 +17449,7 @@
         <v>13</v>
       </c>
       <c r="I583" s="4">
-        <v>2317</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="584" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17466,10 +17466,10 @@
         <v>11</v>
       </c>
       <c r="E584" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F584" s="3">
-        <v>45806</v>
+        <v>45811</v>
       </c>
       <c r="G584" s="1" t="s">
         <v>12</v>
@@ -17478,7 +17478,7 @@
         <v>13</v>
       </c>
       <c r="I584" s="4">
-        <v>2503</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="585" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17489,25 +17489,25 @@
         <v>20</v>
       </c>
       <c r="C585" s="2">
-        <v>34.5</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="D585" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E585" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F585" s="3">
-        <v>45811</v>
+        <v>45813</v>
       </c>
       <c r="G585" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H585" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I585" s="4">
-        <v>2508</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="586" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17518,25 +17518,25 @@
         <v>20</v>
       </c>
       <c r="C586" s="2">
-        <v>32.799999999999997</v>
+        <v>34.5</v>
       </c>
       <c r="D586" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E586" s="2">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F586" s="3">
-        <v>45813</v>
+        <v>45819</v>
       </c>
       <c r="G586" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H586" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I586" s="4">
-        <v>2503</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="587" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17553,7 +17553,7 @@
         <v>11</v>
       </c>
       <c r="E587" s="2">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="F587" s="3">
         <v>45819</v>
@@ -17565,7 +17565,7 @@
         <v>13</v>
       </c>
       <c r="I587" s="4">
-        <v>2407</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="588" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17576,16 +17576,16 @@
         <v>20</v>
       </c>
       <c r="C588" s="2">
-        <v>34.5</v>
+        <v>34.9</v>
       </c>
       <c r="D588" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E588" s="2">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="F588" s="3">
-        <v>45819</v>
+        <v>45827</v>
       </c>
       <c r="G588" s="1" t="s">
         <v>12</v>
@@ -17594,7 +17594,7 @@
         <v>13</v>
       </c>
       <c r="I588" s="4">
-        <v>2412</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="589" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17611,10 +17611,10 @@
         <v>11</v>
       </c>
       <c r="E589" s="2">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="F589" s="3">
-        <v>45827</v>
+        <v>45832</v>
       </c>
       <c r="G589" s="1" t="s">
         <v>12</v>
@@ -17623,7 +17623,7 @@
         <v>13</v>
       </c>
       <c r="I589" s="4">
-        <v>2317</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="590" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17640,10 +17640,10 @@
         <v>11</v>
       </c>
       <c r="E590" s="2">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="F590" s="3">
-        <v>45832</v>
+        <v>45834</v>
       </c>
       <c r="G590" s="1" t="s">
         <v>12</v>
@@ -17652,7 +17652,7 @@
         <v>13</v>
       </c>
       <c r="I590" s="4">
-        <v>2413</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="591" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17669,10 +17669,10 @@
         <v>11</v>
       </c>
       <c r="E591" s="2">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="F591" s="3">
-        <v>45834</v>
+        <v>45840</v>
       </c>
       <c r="G591" s="1" t="s">
         <v>12</v>
@@ -17681,7 +17681,7 @@
         <v>13</v>
       </c>
       <c r="I591" s="4">
-        <v>2508</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="592" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17698,7 +17698,7 @@
         <v>11</v>
       </c>
       <c r="E592" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F592" s="3">
         <v>45840</v>
@@ -17707,10 +17707,10 @@
         <v>12</v>
       </c>
       <c r="H592" s="1" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="I592" s="4">
-        <v>2413</v>
+        <v>9987</v>
       </c>
     </row>
     <row r="593" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17727,7 +17727,7 @@
         <v>11</v>
       </c>
       <c r="E593" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F593" s="3">
         <v>45840</v>
@@ -17756,19 +17756,19 @@
         <v>11</v>
       </c>
       <c r="E594" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F594" s="3">
-        <v>45840</v>
+        <v>45841</v>
       </c>
       <c r="G594" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H594" s="1" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="I594" s="4">
-        <v>9987</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="595" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17785,10 +17785,10 @@
         <v>11</v>
       </c>
       <c r="E595" s="2">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F595" s="3">
-        <v>45841</v>
+        <v>45856</v>
       </c>
       <c r="G595" s="1" t="s">
         <v>12</v>
@@ -17797,7 +17797,7 @@
         <v>13</v>
       </c>
       <c r="I595" s="4">
-        <v>2503</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="596" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17814,10 +17814,10 @@
         <v>11</v>
       </c>
       <c r="E596" s="2">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F596" s="3">
-        <v>45856</v>
+        <v>45860</v>
       </c>
       <c r="G596" s="1" t="s">
         <v>12</v>
@@ -17826,7 +17826,7 @@
         <v>13</v>
       </c>
       <c r="I596" s="4">
-        <v>2411</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="597" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17843,10 +17843,10 @@
         <v>11</v>
       </c>
       <c r="E597" s="2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F597" s="3">
-        <v>45860</v>
+        <v>45866</v>
       </c>
       <c r="G597" s="1" t="s">
         <v>12</v>
@@ -17872,10 +17872,10 @@
         <v>11</v>
       </c>
       <c r="E598" s="2">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F598" s="3">
-        <v>45866</v>
+        <v>45869</v>
       </c>
       <c r="G598" s="1" t="s">
         <v>12</v>
@@ -17884,7 +17884,7 @@
         <v>13</v>
       </c>
       <c r="I598" s="4">
-        <v>2317</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="599" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17901,10 +17901,10 @@
         <v>11</v>
       </c>
       <c r="E599" s="2">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="F599" s="3">
-        <v>45869</v>
+        <v>45875</v>
       </c>
       <c r="G599" s="1" t="s">
         <v>12</v>
@@ -17913,7 +17913,7 @@
         <v>13</v>
       </c>
       <c r="I599" s="4">
-        <v>2508</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="600" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17924,16 +17924,16 @@
         <v>20</v>
       </c>
       <c r="C600" s="2">
-        <v>34.9</v>
+        <v>34.75</v>
       </c>
       <c r="D600" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E600" s="2">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="F600" s="3">
-        <v>45875</v>
+        <v>45896</v>
       </c>
       <c r="G600" s="1" t="s">
         <v>12</v>
@@ -17942,7 +17942,7 @@
         <v>13</v>
       </c>
       <c r="I600" s="4">
-        <v>2411</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="601" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17959,7 +17959,7 @@
         <v>11</v>
       </c>
       <c r="E601" s="2">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="F601" s="3">
         <v>45896</v>
@@ -17971,7 +17971,7 @@
         <v>13</v>
       </c>
       <c r="I601" s="4">
-        <v>2508</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="602" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17991,7 +17991,7 @@
         <v>100</v>
       </c>
       <c r="F602" s="3">
-        <v>45896</v>
+        <v>45897</v>
       </c>
       <c r="G602" s="1" t="s">
         <v>12</v>
@@ -18000,7 +18000,7 @@
         <v>13</v>
       </c>
       <c r="I602" s="4">
-        <v>2317</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="603" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18017,10 +18017,10 @@
         <v>11</v>
       </c>
       <c r="E603" s="2">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F603" s="3">
-        <v>45897</v>
+        <v>45903</v>
       </c>
       <c r="G603" s="1" t="s">
         <v>12</v>
@@ -18049,7 +18049,7 @@
         <v>50</v>
       </c>
       <c r="F604" s="3">
-        <v>45903</v>
+        <v>45911</v>
       </c>
       <c r="G604" s="1" t="s">
         <v>12</v>
@@ -18069,16 +18069,16 @@
         <v>20</v>
       </c>
       <c r="C605" s="2">
-        <v>34.75</v>
+        <v>37</v>
       </c>
       <c r="D605" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E605" s="2">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F605" s="3">
-        <v>45911</v>
+        <v>45915</v>
       </c>
       <c r="G605" s="1" t="s">
         <v>12</v>
@@ -18087,7 +18087,7 @@
         <v>13</v>
       </c>
       <c r="I605" s="4">
-        <v>2411</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="606" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18107,7 +18107,7 @@
         <v>100</v>
       </c>
       <c r="F606" s="3">
-        <v>45915</v>
+        <v>45919</v>
       </c>
       <c r="G606" s="1" t="s">
         <v>12</v>
@@ -18116,7 +18116,7 @@
         <v>13</v>
       </c>
       <c r="I606" s="4">
-        <v>2317</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="607" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18133,7 +18133,7 @@
         <v>11</v>
       </c>
       <c r="E607" s="2">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F607" s="3">
         <v>45919</v>
@@ -18145,7 +18145,7 @@
         <v>13</v>
       </c>
       <c r="I607" s="4">
-        <v>2411</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="608" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18162,10 +18162,10 @@
         <v>11</v>
       </c>
       <c r="E608" s="2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F608" s="3">
-        <v>45919</v>
+        <v>45924</v>
       </c>
       <c r="G608" s="1" t="s">
         <v>12</v>
@@ -18174,7 +18174,7 @@
         <v>13</v>
       </c>
       <c r="I608" s="4">
-        <v>2512</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="609" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18185,16 +18185,16 @@
         <v>20</v>
       </c>
       <c r="C609" s="2">
-        <v>37</v>
+        <v>39.9</v>
       </c>
       <c r="D609" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E609" s="2">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="F609" s="3">
-        <v>45924</v>
+        <v>45938</v>
       </c>
       <c r="G609" s="1" t="s">
         <v>12</v>
@@ -18203,7 +18203,7 @@
         <v>13</v>
       </c>
       <c r="I609" s="4">
-        <v>2511</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="610" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18214,16 +18214,16 @@
         <v>20</v>
       </c>
       <c r="C610" s="2">
-        <v>39.9</v>
+        <v>37.950000000000003</v>
       </c>
       <c r="D610" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E610" s="2">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F610" s="3">
-        <v>45938</v>
+        <v>45957</v>
       </c>
       <c r="G610" s="1" t="s">
         <v>12</v>
@@ -18232,7 +18232,7 @@
         <v>13</v>
       </c>
       <c r="I610" s="4">
-        <v>2317</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="611" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18243,16 +18243,16 @@
         <v>20</v>
       </c>
       <c r="C611" s="2">
-        <v>37.950000000000003</v>
+        <v>37.9</v>
       </c>
       <c r="D611" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E611" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F611" s="3">
-        <v>45957</v>
+        <v>45961</v>
       </c>
       <c r="G611" s="1" t="s">
         <v>12</v>
@@ -18261,7 +18261,7 @@
         <v>13</v>
       </c>
       <c r="I611" s="4">
-        <v>2512</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="612" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18278,7 +18278,7 @@
         <v>11</v>
       </c>
       <c r="E612" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F612" s="3">
         <v>45961</v>
@@ -18301,16 +18301,16 @@
         <v>20</v>
       </c>
       <c r="C613" s="2">
-        <v>37.9</v>
+        <v>37.950000000000003</v>
       </c>
       <c r="D613" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E613" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F613" s="3">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="G613" s="1" t="s">
         <v>12</v>
@@ -18319,7 +18319,7 @@
         <v>13</v>
       </c>
       <c r="I613" s="4">
-        <v>2511</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="614" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18336,10 +18336,10 @@
         <v>11</v>
       </c>
       <c r="E614" s="2">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F614" s="3">
-        <v>45964</v>
+        <v>45968</v>
       </c>
       <c r="G614" s="1" t="s">
         <v>12</v>
@@ -18348,7 +18348,7 @@
         <v>13</v>
       </c>
       <c r="I614" s="4">
-        <v>2317</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="615" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18359,16 +18359,16 @@
         <v>20</v>
       </c>
       <c r="C615" s="2">
-        <v>37.950000000000003</v>
+        <v>37.5</v>
       </c>
       <c r="D615" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E615" s="2">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F615" s="3">
-        <v>45968</v>
+        <v>45978</v>
       </c>
       <c r="G615" s="1" t="s">
         <v>12</v>
@@ -18377,7 +18377,7 @@
         <v>13</v>
       </c>
       <c r="I615" s="4">
-        <v>2511</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="616" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18388,16 +18388,16 @@
         <v>20</v>
       </c>
       <c r="C616" s="2">
-        <v>37.5</v>
+        <v>37.950000000000003</v>
       </c>
       <c r="D616" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E616" s="2">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="F616" s="3">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="G616" s="1" t="s">
         <v>12</v>
@@ -18406,7 +18406,7 @@
         <v>13</v>
       </c>
       <c r="I616" s="4">
-        <v>2317</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="617" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18423,10 +18423,10 @@
         <v>11</v>
       </c>
       <c r="E617" s="2">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F617" s="3">
-        <v>45979</v>
+        <v>45988</v>
       </c>
       <c r="G617" s="1" t="s">
         <v>12</v>
@@ -18435,7 +18435,7 @@
         <v>13</v>
       </c>
       <c r="I617" s="4">
-        <v>2512</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="618" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18452,7 +18452,7 @@
         <v>11</v>
       </c>
       <c r="E618" s="2">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F618" s="3">
         <v>45988</v>
@@ -18464,7 +18464,7 @@
         <v>13</v>
       </c>
       <c r="I618" s="4">
-        <v>2511</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="619" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18481,10 +18481,10 @@
         <v>11</v>
       </c>
       <c r="E619" s="2">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F619" s="3">
-        <v>45988</v>
+        <v>45995</v>
       </c>
       <c r="G619" s="1" t="s">
         <v>12</v>
@@ -18493,7 +18493,7 @@
         <v>13</v>
       </c>
       <c r="I619" s="4">
-        <v>2512</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="620" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18510,10 +18510,10 @@
         <v>11</v>
       </c>
       <c r="E620" s="2">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F620" s="3">
-        <v>45995</v>
+        <v>46001</v>
       </c>
       <c r="G620" s="1" t="s">
         <v>12</v>
@@ -18522,7 +18522,7 @@
         <v>13</v>
       </c>
       <c r="I620" s="4">
-        <v>2511</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="621" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18533,16 +18533,16 @@
         <v>20</v>
       </c>
       <c r="C621" s="2">
-        <v>37.950000000000003</v>
+        <v>37.9</v>
       </c>
       <c r="D621" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E621" s="2">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="F621" s="3">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="G621" s="1" t="s">
         <v>12</v>
@@ -18551,7 +18551,7 @@
         <v>13</v>
       </c>
       <c r="I621" s="4">
-        <v>2512</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="622" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18568,10 +18568,10 @@
         <v>11</v>
       </c>
       <c r="E622" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F622" s="3">
-        <v>46002</v>
+        <v>46029</v>
       </c>
       <c r="G622" s="1" t="s">
         <v>12</v>
@@ -18580,7 +18580,7 @@
         <v>13</v>
       </c>
       <c r="I622" s="4">
-        <v>2511</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="623" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18591,16 +18591,16 @@
         <v>20</v>
       </c>
       <c r="C623" s="2">
-        <v>37.9</v>
+        <v>37.950000000000003</v>
       </c>
       <c r="D623" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E623" s="2">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F623" s="3">
-        <v>46029</v>
+        <v>46037</v>
       </c>
       <c r="G623" s="1" t="s">
         <v>12</v>
@@ -18609,7 +18609,7 @@
         <v>13</v>
       </c>
       <c r="I623" s="4">
-        <v>2317</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="624" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18626,10 +18626,10 @@
         <v>11</v>
       </c>
       <c r="E624" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F624" s="3">
-        <v>46037</v>
+        <v>46050</v>
       </c>
       <c r="G624" s="1" t="s">
         <v>12</v>
@@ -18638,7 +18638,7 @@
         <v>13</v>
       </c>
       <c r="I624" s="4">
-        <v>2516</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="625" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18655,10 +18655,10 @@
         <v>11</v>
       </c>
       <c r="E625" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F625" s="3">
-        <v>46050</v>
+        <v>46055</v>
       </c>
       <c r="G625" s="1" t="s">
         <v>12</v>
@@ -18667,7 +18667,7 @@
         <v>13</v>
       </c>
       <c r="I625" s="4">
-        <v>2317</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="626" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18684,10 +18684,10 @@
         <v>11</v>
       </c>
       <c r="E626" s="2">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F626" s="3">
-        <v>46055</v>
+        <v>46063</v>
       </c>
       <c r="G626" s="1" t="s">
         <v>12</v>
@@ -18713,10 +18713,10 @@
         <v>11</v>
       </c>
       <c r="E627" s="2">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F627" s="3">
-        <v>46063</v>
+        <v>46066</v>
       </c>
       <c r="G627" s="1" t="s">
         <v>12</v>
@@ -18725,7 +18725,7 @@
         <v>13</v>
       </c>
       <c r="I627" s="4">
-        <v>2516</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="628" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18742,10 +18742,10 @@
         <v>11</v>
       </c>
       <c r="E628" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F628" s="3">
-        <v>46066</v>
+        <v>46076</v>
       </c>
       <c r="G628" s="1" t="s">
         <v>12</v>
@@ -18771,7 +18771,7 @@
         <v>11</v>
       </c>
       <c r="E629" s="2">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="F629" s="3">
         <v>46076</v>
@@ -18783,7 +18783,7 @@
         <v>13</v>
       </c>
       <c r="I629" s="4">
-        <v>2317</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="630" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18800,10 +18800,10 @@
         <v>11</v>
       </c>
       <c r="E630" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F630" s="3">
-        <v>46076</v>
+        <v>46094</v>
       </c>
       <c r="G630" s="1" t="s">
         <v>12</v>
@@ -18812,7 +18812,7 @@
         <v>13</v>
       </c>
       <c r="I630" s="4">
-        <v>2512</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="631" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18823,7 +18823,7 @@
         <v>20</v>
       </c>
       <c r="C631" s="2">
-        <v>37.950000000000003</v>
+        <v>38.9</v>
       </c>
       <c r="D631" s="1" t="s">
         <v>11</v>
@@ -18832,7 +18832,7 @@
         <v>10</v>
       </c>
       <c r="F631" s="3">
-        <v>46094</v>
+        <v>46118</v>
       </c>
       <c r="G631" s="1" t="s">
         <v>12</v>
@@ -18861,7 +18861,7 @@
         <v>10</v>
       </c>
       <c r="F632" s="3">
-        <v>46118</v>
+        <v>46132</v>
       </c>
       <c r="G632" s="1" t="s">
         <v>12</v>
@@ -18890,7 +18890,7 @@
         <v>10</v>
       </c>
       <c r="F633" s="3">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="G633" s="1" t="s">
         <v>12</v>
@@ -18916,10 +18916,10 @@
         <v>11</v>
       </c>
       <c r="E634" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F634" s="3">
-        <v>46134</v>
+        <v>46142</v>
       </c>
       <c r="G634" s="1" t="s">
         <v>12</v>
@@ -18928,7 +18928,7 @@
         <v>13</v>
       </c>
       <c r="I634" s="4">
-        <v>2516</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="635" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18945,10 +18945,10 @@
         <v>11</v>
       </c>
       <c r="E635" s="2">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F635" s="3">
-        <v>46142</v>
+        <v>46153</v>
       </c>
       <c r="G635" s="1" t="s">
         <v>12</v>
@@ -18957,7 +18957,7 @@
         <v>13</v>
       </c>
       <c r="I635" s="4">
-        <v>2601</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="636" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18974,7 +18974,7 @@
         <v>11</v>
       </c>
       <c r="E636" s="2">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F636" s="3">
         <v>46153</v>
@@ -18986,7 +18986,7 @@
         <v>13</v>
       </c>
       <c r="I636" s="4">
-        <v>2512</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="637" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19003,7 +19003,7 @@
         <v>11</v>
       </c>
       <c r="E637" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F637" s="3">
         <v>46153</v>
@@ -19015,7 +19015,7 @@
         <v>13</v>
       </c>
       <c r="I637" s="4">
-        <v>2516</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="638" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19032,10 +19032,10 @@
         <v>11</v>
       </c>
       <c r="E638" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F638" s="3">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="G638" s="1" t="s">
         <v>12</v>
@@ -19044,7 +19044,7 @@
         <v>13</v>
       </c>
       <c r="I638" s="4">
-        <v>2606</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="639" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19061,10 +19061,10 @@
         <v>11</v>
       </c>
       <c r="E639" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F639" s="3">
-        <v>46155</v>
+        <v>46167</v>
       </c>
       <c r="G639" s="1" t="s">
         <v>12</v>
@@ -19073,7 +19073,7 @@
         <v>13</v>
       </c>
       <c r="I639" s="4">
-        <v>2211</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="640" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19084,13 +19084,13 @@
         <v>20</v>
       </c>
       <c r="C640" s="2">
-        <v>38.9</v>
+        <v>37.950000000000003</v>
       </c>
       <c r="D640" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E640" s="2">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F640" s="3">
         <v>46167</v>
@@ -19102,7 +19102,7 @@
         <v>13</v>
       </c>
       <c r="I640" s="4">
-        <v>2516</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="641" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19113,7 +19113,7 @@
         <v>20</v>
       </c>
       <c r="C641" s="2">
-        <v>37.950000000000003</v>
+        <v>38.9</v>
       </c>
       <c r="D641" s="1" t="s">
         <v>11</v>
@@ -19122,7 +19122,7 @@
         <v>50</v>
       </c>
       <c r="F641" s="3">
-        <v>46167</v>
+        <v>46171</v>
       </c>
       <c r="G641" s="1" t="s">
         <v>12</v>
@@ -19131,7 +19131,7 @@
         <v>13</v>
       </c>
       <c r="I641" s="4">
-        <v>2601</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="642" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19148,10 +19148,10 @@
         <v>11</v>
       </c>
       <c r="E642" s="2">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F642" s="3">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="G642" s="1" t="s">
         <v>12</v>
@@ -19160,7 +19160,7 @@
         <v>13</v>
       </c>
       <c r="I642" s="4">
-        <v>2606</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="643" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19177,10 +19177,10 @@
         <v>11</v>
       </c>
       <c r="E643" s="2">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F643" s="3">
-        <v>46174</v>
+        <v>46188</v>
       </c>
       <c r="G643" s="1" t="s">
         <v>12</v>
@@ -19189,7 +19189,7 @@
         <v>13</v>
       </c>
       <c r="I643" s="4">
-        <v>2516</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="644" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19206,10 +19206,10 @@
         <v>11</v>
       </c>
       <c r="E644" s="2">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="F644" s="3">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="G644" s="1" t="s">
         <v>12</v>
@@ -19218,7 +19218,7 @@
         <v>13</v>
       </c>
       <c r="I644" s="4">
-        <v>2601</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="645" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19235,10 +19235,10 @@
         <v>11</v>
       </c>
       <c r="E645" s="2">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F645" s="3">
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="G645" s="1" t="s">
         <v>12</v>
@@ -19247,7 +19247,7 @@
         <v>13</v>
       </c>
       <c r="I645" s="4">
-        <v>2605</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="646" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19264,10 +19264,10 @@
         <v>11</v>
       </c>
       <c r="E646" s="2">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="F646" s="3">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="G646" s="1" t="s">
         <v>12</v>
@@ -19276,7 +19276,7 @@
         <v>13</v>
       </c>
       <c r="I646" s="4">
-        <v>2606</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="647" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19293,10 +19293,10 @@
         <v>11</v>
       </c>
       <c r="E647" s="2">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="F647" s="3">
-        <v>46197</v>
+        <v>46211</v>
       </c>
       <c r="G647" s="1" t="s">
         <v>12</v>
@@ -19305,7 +19305,7 @@
         <v>13</v>
       </c>
       <c r="I647" s="4">
-        <v>2602</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="648" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19325,7 +19325,7 @@
         <v>10</v>
       </c>
       <c r="F648" s="3">
-        <v>46211</v>
+        <v>46225</v>
       </c>
       <c r="G648" s="1" t="s">
         <v>12</v>
@@ -19345,25 +19345,25 @@
         <v>20</v>
       </c>
       <c r="C649" s="2">
-        <v>38.9</v>
+        <v>37.200000000000003</v>
       </c>
       <c r="D649" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E649" s="2">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="F649" s="3">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="G649" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H649" s="1" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="I649" s="4">
-        <v>2605</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="650" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19374,25 +19374,25 @@
         <v>20</v>
       </c>
       <c r="C650" s="2">
-        <v>37.200000000000003</v>
+        <v>38.9</v>
       </c>
       <c r="D650" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E650" s="2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F650" s="3">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="G650" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H650" s="1" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="I650" s="4">
-        <v>2606</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="651" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19438,7 +19438,7 @@
         <v>11</v>
       </c>
       <c r="E652" s="2">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F652" s="3">
         <v>46234</v>
@@ -19450,7 +19450,7 @@
         <v>13</v>
       </c>
       <c r="I652" s="4">
-        <v>2601</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="653" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19461,16 +19461,16 @@
         <v>20</v>
       </c>
       <c r="C653" s="2">
-        <v>38.9</v>
+        <v>40</v>
       </c>
       <c r="D653" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E653" s="2">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F653" s="3">
-        <v>46234</v>
+        <v>46241</v>
       </c>
       <c r="G653" s="1" t="s">
         <v>12</v>
@@ -19479,7 +19479,7 @@
         <v>13</v>
       </c>
       <c r="I653" s="4">
-        <v>2602</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="654" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19490,16 +19490,16 @@
         <v>20</v>
       </c>
       <c r="C654" s="2">
-        <v>40</v>
+        <v>38.9</v>
       </c>
       <c r="D654" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E654" s="2">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="F654" s="3">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="G654" s="1" t="s">
         <v>12</v>
@@ -19508,7 +19508,7 @@
         <v>13</v>
       </c>
       <c r="I654" s="4">
-        <v>2606</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="655" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19519,25 +19519,25 @@
         <v>20</v>
       </c>
       <c r="C655" s="2">
-        <v>38.9</v>
+        <v>41.88</v>
       </c>
       <c r="D655" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E655" s="2">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="F655" s="3">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="G655" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H655" s="1" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="I655" s="4">
-        <v>2602</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="656" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19548,25 +19548,25 @@
         <v>20</v>
       </c>
       <c r="C656" s="2">
-        <v>41.88</v>
+        <v>38.9</v>
       </c>
       <c r="D656" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E656" s="2">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F656" s="3">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="G656" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H656" s="1" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="I656" s="4">
-        <v>2601</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="657" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19577,25 +19577,25 @@
         <v>20</v>
       </c>
       <c r="C657" s="2">
-        <v>38.9</v>
+        <v>36.99</v>
       </c>
       <c r="D657" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E657" s="2">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F657" s="3">
-        <v>46248</v>
+        <v>46254</v>
       </c>
       <c r="G657" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H657" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I657" s="4">
-        <v>2605</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="658" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19606,13 +19606,13 @@
         <v>20</v>
       </c>
       <c r="C658" s="2">
-        <v>36.99</v>
+        <v>37</v>
       </c>
       <c r="D658" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E658" s="2">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F658" s="3">
         <v>46254</v>
@@ -19624,7 +19624,7 @@
         <v>16</v>
       </c>
       <c r="I658" s="4">
-        <v>2601</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="659" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19635,16 +19635,16 @@
         <v>20</v>
       </c>
       <c r="C659" s="2">
-        <v>37</v>
+        <v>36.99</v>
       </c>
       <c r="D659" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E659" s="2">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="F659" s="3">
-        <v>46254</v>
+        <v>46259</v>
       </c>
       <c r="G659" s="1" t="s">
         <v>12</v>
@@ -19653,7 +19653,7 @@
         <v>16</v>
       </c>
       <c r="I659" s="4">
-        <v>2607</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="660" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19664,25 +19664,25 @@
         <v>20</v>
       </c>
       <c r="C660" s="2">
-        <v>36.99</v>
+        <v>38.880000000000003</v>
       </c>
       <c r="D660" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E660" s="2">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F660" s="3">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="G660" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H660" s="1" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="I660" s="4">
-        <v>2605</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="661" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19693,7 +19693,7 @@
         <v>20</v>
       </c>
       <c r="C661" s="2">
-        <v>38.880000000000003</v>
+        <v>40</v>
       </c>
       <c r="D661" s="1" t="s">
         <v>11</v>
@@ -19702,13 +19702,13 @@
         <v>100</v>
       </c>
       <c r="F661" s="3">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="G661" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H661" s="1" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="I661" s="4">
         <v>2606</v>
@@ -19722,7 +19722,7 @@
         <v>20</v>
       </c>
       <c r="C662" s="2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D662" s="1" t="s">
         <v>11</v>
@@ -19737,7 +19737,7 @@
         <v>12</v>
       </c>
       <c r="H662" s="1" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="I662" s="4">
         <v>2606</v>
@@ -19751,25 +19751,25 @@
         <v>20</v>
       </c>
       <c r="C663" s="2">
-        <v>36</v>
+        <v>38.9788</v>
       </c>
       <c r="D663" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E663" s="2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F663" s="3">
-        <v>46266</v>
+        <v>46273</v>
       </c>
       <c r="G663" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H663" s="1" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="I663" s="4">
-        <v>2606</v>
+        <v>2611</v>
       </c>
     </row>
     <row r="664" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19780,16 +19780,16 @@
         <v>20</v>
       </c>
       <c r="C664" s="2">
-        <v>38.9788</v>
+        <v>38.620699999999999</v>
       </c>
       <c r="D664" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E664" s="2">
-        <v>200</v>
+        <v>81</v>
       </c>
       <c r="F664" s="3">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="G664" s="1" t="s">
         <v>12</v>
@@ -19798,7 +19798,7 @@
         <v>16</v>
       </c>
       <c r="I664" s="4">
-        <v>2611</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="665" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19809,16 +19809,16 @@
         <v>20</v>
       </c>
       <c r="C665" s="2">
-        <v>38.620699999999999</v>
+        <v>38.1</v>
       </c>
       <c r="D665" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E665" s="2">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="F665" s="3">
-        <v>46274</v>
+        <v>46276</v>
       </c>
       <c r="G665" s="1" t="s">
         <v>12</v>
@@ -19827,7 +19827,7 @@
         <v>16</v>
       </c>
       <c r="I665" s="4">
-        <v>2605</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="666" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19838,13 +19838,13 @@
         <v>20</v>
       </c>
       <c r="C666" s="2">
-        <v>38.1</v>
+        <v>40.9</v>
       </c>
       <c r="D666" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E666" s="2">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F666" s="3">
         <v>46276</v>
@@ -19853,10 +19853,10 @@
         <v>12</v>
       </c>
       <c r="H666" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I666" s="4">
-        <v>2601</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="667" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19867,25 +19867,25 @@
         <v>20</v>
       </c>
       <c r="C667" s="2">
-        <v>40.9</v>
+        <v>38.1</v>
       </c>
       <c r="D667" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E667" s="2">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="F667" s="3">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="G667" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H667" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I667" s="4">
-        <v>2612</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="668" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19902,10 +19902,10 @@
         <v>11</v>
       </c>
       <c r="E668" s="2">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="F668" s="3">
-        <v>46283</v>
+        <v>46287</v>
       </c>
       <c r="G668" s="1" t="s">
         <v>12</v>
@@ -19914,7 +19914,7 @@
         <v>16</v>
       </c>
       <c r="I668" s="4">
-        <v>2601</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="669" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19931,10 +19931,10 @@
         <v>11</v>
       </c>
       <c r="E669" s="2">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="F669" s="3">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="G669" s="1" t="s">
         <v>12</v>
@@ -19943,7 +19943,7 @@
         <v>16</v>
       </c>
       <c r="I669" s="4">
-        <v>2607</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="670" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19960,10 +19960,10 @@
         <v>11</v>
       </c>
       <c r="E670" s="2">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F670" s="3">
-        <v>46289</v>
+        <v>46297</v>
       </c>
       <c r="G670" s="1" t="s">
         <v>12</v>
@@ -19972,18 +19972,18 @@
         <v>16</v>
       </c>
       <c r="I670" s="4">
-        <v>2612</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="671" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B671" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C671" s="2">
-        <v>38.1</v>
+        <v>4.8</v>
       </c>
       <c r="D671" s="1" t="s">
         <v>11</v>
@@ -19992,16 +19992,16 @@
         <v>50</v>
       </c>
       <c r="F671" s="3">
-        <v>46297</v>
+        <v>45660</v>
       </c>
       <c r="G671" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H671" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I671" s="4">
-        <v>2605</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="672" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20018,10 +20018,10 @@
         <v>11</v>
       </c>
       <c r="E672" s="2">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F672" s="3">
-        <v>45660</v>
+        <v>45672</v>
       </c>
       <c r="G672" s="1" t="s">
         <v>12</v>
@@ -20047,7 +20047,7 @@
         <v>11</v>
       </c>
       <c r="E673" s="2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F673" s="3">
         <v>45672</v>
@@ -20059,7 +20059,7 @@
         <v>13</v>
       </c>
       <c r="I673" s="4">
-        <v>2317</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="674" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20070,25 +20070,25 @@
         <v>10</v>
       </c>
       <c r="C674" s="2">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="D674" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E674" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F674" s="3">
-        <v>45672</v>
+        <v>45674</v>
       </c>
       <c r="G674" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H674" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I674" s="4">
-        <v>2407</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="675" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20099,22 +20099,22 @@
         <v>10</v>
       </c>
       <c r="C675" s="2">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="D675" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E675" s="2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F675" s="3">
-        <v>45674</v>
+        <v>45694</v>
       </c>
       <c r="G675" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H675" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I675" s="4">
         <v>2411</v>
@@ -20137,7 +20137,7 @@
         <v>200</v>
       </c>
       <c r="F676" s="3">
-        <v>45694</v>
+        <v>45706</v>
       </c>
       <c r="G676" s="1" t="s">
         <v>12</v>
@@ -20157,7 +20157,7 @@
         <v>10</v>
       </c>
       <c r="C677" s="2">
-        <v>4.8</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="D677" s="1" t="s">
         <v>11</v>
@@ -20166,7 +20166,7 @@
         <v>200</v>
       </c>
       <c r="F677" s="3">
-        <v>45706</v>
+        <v>45709</v>
       </c>
       <c r="G677" s="1" t="s">
         <v>12</v>
@@ -20186,16 +20186,16 @@
         <v>10</v>
       </c>
       <c r="C678" s="2">
-        <v>4.8899999999999997</v>
+        <v>5.8</v>
       </c>
       <c r="D678" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E678" s="2">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F678" s="3">
-        <v>45709</v>
+        <v>45730</v>
       </c>
       <c r="G678" s="1" t="s">
         <v>12</v>
@@ -20204,7 +20204,7 @@
         <v>13</v>
       </c>
       <c r="I678" s="4">
-        <v>2411</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="679" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20224,7 +20224,7 @@
         <v>300</v>
       </c>
       <c r="F679" s="3">
-        <v>45730</v>
+        <v>45754</v>
       </c>
       <c r="G679" s="1" t="s">
         <v>12</v>
@@ -20250,10 +20250,10 @@
         <v>11</v>
       </c>
       <c r="E680" s="2">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="F680" s="3">
-        <v>45754</v>
+        <v>45775</v>
       </c>
       <c r="G680" s="1" t="s">
         <v>12</v>
@@ -20279,10 +20279,10 @@
         <v>11</v>
       </c>
       <c r="E681" s="2">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="F681" s="3">
-        <v>45775</v>
+        <v>45856</v>
       </c>
       <c r="G681" s="1" t="s">
         <v>12</v>
@@ -20291,7 +20291,7 @@
         <v>13</v>
       </c>
       <c r="I681" s="4">
-        <v>2317</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="682" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20308,10 +20308,10 @@
         <v>11</v>
       </c>
       <c r="E682" s="2">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F682" s="3">
-        <v>45856</v>
+        <v>45897</v>
       </c>
       <c r="G682" s="1" t="s">
         <v>12</v>
@@ -20337,10 +20337,10 @@
         <v>11</v>
       </c>
       <c r="E683" s="2">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F683" s="3">
-        <v>45897</v>
+        <v>45924</v>
       </c>
       <c r="G683" s="1" t="s">
         <v>12</v>
@@ -20349,7 +20349,7 @@
         <v>13</v>
       </c>
       <c r="I683" s="4">
-        <v>2411</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="684" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20366,10 +20366,10 @@
         <v>11</v>
       </c>
       <c r="E684" s="2">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="F684" s="3">
-        <v>45924</v>
+        <v>45930</v>
       </c>
       <c r="G684" s="1" t="s">
         <v>12</v>
@@ -20378,7 +20378,7 @@
         <v>13</v>
       </c>
       <c r="I684" s="4">
-        <v>2317</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="685" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20395,10 +20395,10 @@
         <v>11</v>
       </c>
       <c r="E685" s="2">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="F685" s="3">
-        <v>45930</v>
+        <v>45938</v>
       </c>
       <c r="G685" s="1" t="s">
         <v>12</v>
@@ -20407,7 +20407,7 @@
         <v>13</v>
       </c>
       <c r="I685" s="4">
-        <v>2411</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="686" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20424,10 +20424,10 @@
         <v>11</v>
       </c>
       <c r="E686" s="2">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="F686" s="3">
-        <v>45938</v>
+        <v>45954</v>
       </c>
       <c r="G686" s="1" t="s">
         <v>12</v>
@@ -20453,10 +20453,10 @@
         <v>11</v>
       </c>
       <c r="E687" s="2">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F687" s="3">
-        <v>45954</v>
+        <v>45964</v>
       </c>
       <c r="G687" s="1" t="s">
         <v>12</v>
@@ -20482,10 +20482,10 @@
         <v>11</v>
       </c>
       <c r="E688" s="2">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="F688" s="3">
-        <v>45964</v>
+        <v>45972</v>
       </c>
       <c r="G688" s="1" t="s">
         <v>12</v>
@@ -20494,7 +20494,7 @@
         <v>13</v>
       </c>
       <c r="I688" s="4">
-        <v>2317</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="689" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20511,10 +20511,10 @@
         <v>11</v>
       </c>
       <c r="E689" s="2">
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="F689" s="3">
-        <v>45972</v>
+        <v>45978</v>
       </c>
       <c r="G689" s="1" t="s">
         <v>12</v>
@@ -20523,7 +20523,7 @@
         <v>13</v>
       </c>
       <c r="I689" s="4">
-        <v>2411</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="690" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20540,10 +20540,10 @@
         <v>11</v>
       </c>
       <c r="E690" s="2">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="F690" s="3">
-        <v>45978</v>
+        <v>45981</v>
       </c>
       <c r="G690" s="1" t="s">
         <v>12</v>
@@ -20552,7 +20552,7 @@
         <v>13</v>
       </c>
       <c r="I690" s="4">
-        <v>2317</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="691" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20569,10 +20569,10 @@
         <v>11</v>
       </c>
       <c r="E691" s="2">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F691" s="3">
-        <v>45981</v>
+        <v>46006</v>
       </c>
       <c r="G691" s="1" t="s">
         <v>12</v>
@@ -20581,7 +20581,7 @@
         <v>13</v>
       </c>
       <c r="I691" s="4">
-        <v>2516</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="692" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20598,10 +20598,10 @@
         <v>11</v>
       </c>
       <c r="E692" s="2">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F692" s="3">
-        <v>46006</v>
+        <v>46044</v>
       </c>
       <c r="G692" s="1" t="s">
         <v>12</v>
@@ -20627,10 +20627,10 @@
         <v>11</v>
       </c>
       <c r="E693" s="2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F693" s="3">
-        <v>46044</v>
+        <v>46050</v>
       </c>
       <c r="G693" s="1" t="s">
         <v>12</v>
@@ -20656,10 +20656,10 @@
         <v>11</v>
       </c>
       <c r="E694" s="2">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F694" s="3">
-        <v>46050</v>
+        <v>46058</v>
       </c>
       <c r="G694" s="1" t="s">
         <v>12</v>
@@ -20685,10 +20685,10 @@
         <v>11</v>
       </c>
       <c r="E695" s="2">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F695" s="3">
-        <v>46058</v>
+        <v>46065</v>
       </c>
       <c r="G695" s="1" t="s">
         <v>12</v>
@@ -20697,7 +20697,7 @@
         <v>13</v>
       </c>
       <c r="I695" s="4">
-        <v>2317</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="696" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20714,10 +20714,10 @@
         <v>11</v>
       </c>
       <c r="E696" s="2">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F696" s="3">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="G696" s="1" t="s">
         <v>12</v>
@@ -20726,7 +20726,7 @@
         <v>13</v>
       </c>
       <c r="I696" s="4">
-        <v>2516</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="697" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20746,7 +20746,7 @@
         <v>50</v>
       </c>
       <c r="F697" s="3">
-        <v>46066</v>
+        <v>46118</v>
       </c>
       <c r="G697" s="1" t="s">
         <v>12</v>
@@ -20755,7 +20755,7 @@
         <v>13</v>
       </c>
       <c r="I697" s="4">
-        <v>2317</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="698" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20766,16 +20766,16 @@
         <v>10</v>
       </c>
       <c r="C698" s="2">
-        <v>5.8</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="D698" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E698" s="2">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F698" s="3">
-        <v>46118</v>
+        <v>46134</v>
       </c>
       <c r="G698" s="1" t="s">
         <v>12</v>
@@ -20795,16 +20795,16 @@
         <v>10</v>
       </c>
       <c r="C699" s="2">
-        <v>5.0999999999999996</v>
+        <v>5.3</v>
       </c>
       <c r="D699" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E699" s="2">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F699" s="3">
-        <v>46134</v>
+        <v>46171</v>
       </c>
       <c r="G699" s="1" t="s">
         <v>12</v>
@@ -20813,7 +20813,7 @@
         <v>13</v>
       </c>
       <c r="I699" s="4">
-        <v>2516</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="700" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20824,16 +20824,16 @@
         <v>10</v>
       </c>
       <c r="C700" s="2">
-        <v>5.3</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="D700" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E700" s="2">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="F700" s="3">
-        <v>46171</v>
+        <v>46231</v>
       </c>
       <c r="G700" s="1" t="s">
         <v>12</v>
@@ -20842,7 +20842,7 @@
         <v>13</v>
       </c>
       <c r="I700" s="4">
-        <v>2606</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="701" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20853,25 +20853,25 @@
         <v>10</v>
       </c>
       <c r="C701" s="2">
-        <v>5.0999999999999996</v>
+        <v>5.8</v>
       </c>
       <c r="D701" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E701" s="2">
-        <v>40</v>
+        <v>250</v>
       </c>
       <c r="F701" s="3">
-        <v>46231</v>
+        <v>46254</v>
       </c>
       <c r="G701" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H701" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I701" s="4">
-        <v>2317</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="702" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20888,10 +20888,10 @@
         <v>11</v>
       </c>
       <c r="E702" s="2">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="F702" s="3">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="G702" s="1" t="s">
         <v>12</v>
@@ -20900,7 +20900,7 @@
         <v>16</v>
       </c>
       <c r="I702" s="4">
-        <v>2607</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="703" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20917,10 +20917,10 @@
         <v>11</v>
       </c>
       <c r="E703" s="2">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="F703" s="3">
-        <v>46255</v>
+        <v>46275</v>
       </c>
       <c r="G703" s="1" t="s">
         <v>12</v>
@@ -20929,7 +20929,7 @@
         <v>16</v>
       </c>
       <c r="I703" s="4">
-        <v>2601</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="704" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20940,25 +20940,25 @@
         <v>10</v>
       </c>
       <c r="C704" s="2">
-        <v>5.8</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="D704" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E704" s="2">
-        <v>220</v>
+        <v>10</v>
       </c>
       <c r="F704" s="3">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="G704" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H704" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I704" s="4">
-        <v>2607</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="705" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20969,25 +20969,25 @@
         <v>10</v>
       </c>
       <c r="C705" s="2">
-        <v>5.0999999999999996</v>
+        <v>5.8</v>
       </c>
       <c r="D705" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E705" s="2">
-        <v>10</v>
+        <v>190</v>
       </c>
       <c r="F705" s="3">
-        <v>46276</v>
+        <v>46287</v>
       </c>
       <c r="G705" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H705" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I705" s="4">
-        <v>2612</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="706" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21004,10 +21004,10 @@
         <v>11</v>
       </c>
       <c r="E706" s="2">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="F706" s="3">
-        <v>46287</v>
+        <v>46297</v>
       </c>
       <c r="G706" s="1" t="s">
         <v>12</v>
@@ -21021,22 +21021,22 @@
     </row>
     <row r="707" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A707" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B707" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C707" s="2">
-        <v>5.8</v>
+        <v>29.8</v>
       </c>
       <c r="D707" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E707" s="2">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F707" s="3">
-        <v>46297</v>
+        <v>45660</v>
       </c>
       <c r="G707" s="1" t="s">
         <v>12</v>
@@ -21045,7 +21045,7 @@
         <v>16</v>
       </c>
       <c r="I707" s="4">
-        <v>2607</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="708" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21056,7 +21056,7 @@
         <v>15</v>
       </c>
       <c r="C708" s="2">
-        <v>29.8</v>
+        <v>28.71</v>
       </c>
       <c r="D708" s="1" t="s">
         <v>11</v>
@@ -21065,16 +21065,16 @@
         <v>100</v>
       </c>
       <c r="F708" s="3">
-        <v>45660</v>
+        <v>45664</v>
       </c>
       <c r="G708" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H708" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I708" s="4">
-        <v>2317</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="709" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21085,16 +21085,16 @@
         <v>15</v>
       </c>
       <c r="C709" s="2">
-        <v>28.71</v>
+        <v>31.9</v>
       </c>
       <c r="D709" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E709" s="2">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F709" s="3">
-        <v>45664</v>
+        <v>45684</v>
       </c>
       <c r="G709" s="1" t="s">
         <v>12</v>
@@ -21103,7 +21103,7 @@
         <v>13</v>
       </c>
       <c r="I709" s="4">
-        <v>2412</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="710" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21120,10 +21120,10 @@
         <v>11</v>
       </c>
       <c r="E710" s="2">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F710" s="3">
-        <v>45684</v>
+        <v>45686</v>
       </c>
       <c r="G710" s="1" t="s">
         <v>12</v>
@@ -21132,7 +21132,7 @@
         <v>13</v>
       </c>
       <c r="I710" s="4">
-        <v>2407</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="711" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21149,10 +21149,10 @@
         <v>11</v>
       </c>
       <c r="E711" s="2">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="F711" s="3">
-        <v>45686</v>
+        <v>45690</v>
       </c>
       <c r="G711" s="1" t="s">
         <v>12</v>
@@ -21161,7 +21161,7 @@
         <v>13</v>
       </c>
       <c r="I711" s="4">
-        <v>2413</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="712" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21178,10 +21178,10 @@
         <v>11</v>
       </c>
       <c r="E712" s="2">
-        <v>70</v>
+        <v>98.576745000000003</v>
       </c>
       <c r="F712" s="3">
-        <v>45690</v>
+        <v>45693</v>
       </c>
       <c r="G712" s="1" t="s">
         <v>12</v>
@@ -21190,7 +21190,7 @@
         <v>13</v>
       </c>
       <c r="I712" s="4">
-        <v>2412</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="713" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21201,13 +21201,13 @@
         <v>15</v>
       </c>
       <c r="C713" s="2">
-        <v>31.9</v>
+        <v>34</v>
       </c>
       <c r="D713" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E713" s="2">
-        <v>98.576745000000003</v>
+        <v>100</v>
       </c>
       <c r="F713" s="3">
         <v>45693</v>
@@ -21216,10 +21216,10 @@
         <v>12</v>
       </c>
       <c r="H713" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="I713" s="4">
-        <v>2407</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="714" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21230,25 +21230,25 @@
         <v>15</v>
       </c>
       <c r="C714" s="2">
-        <v>34</v>
+        <v>29.8</v>
       </c>
       <c r="D714" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E714" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F714" s="3">
-        <v>45693</v>
+        <v>45695</v>
       </c>
       <c r="G714" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H714" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="I714" s="4">
-        <v>2502</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="715" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21259,25 +21259,25 @@
         <v>15</v>
       </c>
       <c r="C715" s="2">
-        <v>29.8</v>
+        <v>31.9</v>
       </c>
       <c r="D715" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E715" s="2">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="F715" s="3">
-        <v>45695</v>
+        <v>45699</v>
       </c>
       <c r="G715" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H715" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I715" s="4">
-        <v>2413</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="716" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21288,25 +21288,25 @@
         <v>15</v>
       </c>
       <c r="C716" s="2">
-        <v>31.9</v>
+        <v>29.8</v>
       </c>
       <c r="D716" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E716" s="2">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F716" s="3">
-        <v>45699</v>
+        <v>45701</v>
       </c>
       <c r="G716" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H716" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I716" s="4">
-        <v>2412</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="717" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21326,7 +21326,7 @@
         <v>50</v>
       </c>
       <c r="F717" s="3">
-        <v>45701</v>
+        <v>45706</v>
       </c>
       <c r="G717" s="1" t="s">
         <v>12</v>
@@ -21335,7 +21335,7 @@
         <v>16</v>
       </c>
       <c r="I717" s="4">
-        <v>2502</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="718" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21346,16 +21346,16 @@
         <v>15</v>
       </c>
       <c r="C718" s="2">
-        <v>29.8</v>
+        <v>32.9</v>
       </c>
       <c r="D718" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E718" s="2">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F718" s="3">
-        <v>45706</v>
+        <v>45722</v>
       </c>
       <c r="G718" s="1" t="s">
         <v>12</v>
@@ -21364,7 +21364,7 @@
         <v>16</v>
       </c>
       <c r="I718" s="4">
-        <v>2503</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="719" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21381,19 +21381,19 @@
         <v>11</v>
       </c>
       <c r="E719" s="2">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F719" s="3">
-        <v>45722</v>
+        <v>45723</v>
       </c>
       <c r="G719" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H719" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I719" s="4">
-        <v>2407</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="720" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21404,7 +21404,7 @@
         <v>15</v>
       </c>
       <c r="C720" s="2">
-        <v>32.9</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="D720" s="1" t="s">
         <v>11</v>
@@ -21413,13 +21413,13 @@
         <v>50</v>
       </c>
       <c r="F720" s="3">
-        <v>45723</v>
+        <v>45737</v>
       </c>
       <c r="G720" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H720" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I720" s="4">
         <v>2412</v>
@@ -21433,25 +21433,25 @@
         <v>15</v>
       </c>
       <c r="C721" s="2">
-        <v>34.799999999999997</v>
+        <v>33.9</v>
       </c>
       <c r="D721" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E721" s="2">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="F721" s="3">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="G721" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H721" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I721" s="4">
-        <v>2412</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="722" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21468,10 +21468,10 @@
         <v>11</v>
       </c>
       <c r="E722" s="2">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="F722" s="3">
-        <v>45740</v>
+        <v>45743</v>
       </c>
       <c r="G722" s="1" t="s">
         <v>12</v>
@@ -21480,7 +21480,7 @@
         <v>13</v>
       </c>
       <c r="I722" s="4">
-        <v>2413</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="723" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21497,10 +21497,10 @@
         <v>11</v>
       </c>
       <c r="E723" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F723" s="3">
-        <v>45743</v>
+        <v>45747</v>
       </c>
       <c r="G723" s="1" t="s">
         <v>12</v>
@@ -21509,7 +21509,7 @@
         <v>13</v>
       </c>
       <c r="I723" s="4">
-        <v>2503</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="724" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21526,19 +21526,19 @@
         <v>11</v>
       </c>
       <c r="E724" s="2">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="F724" s="3">
-        <v>45747</v>
+        <v>45754</v>
       </c>
       <c r="G724" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H724" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I724" s="4">
-        <v>2412</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="725" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21555,7 +21555,7 @@
         <v>11</v>
       </c>
       <c r="E725" s="2">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="F725" s="3">
         <v>45754</v>
@@ -21564,10 +21564,10 @@
         <v>12</v>
       </c>
       <c r="H725" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I725" s="4">
-        <v>2317</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="726" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21584,10 +21584,10 @@
         <v>11</v>
       </c>
       <c r="E726" s="2">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="F726" s="3">
-        <v>45754</v>
+        <v>45764</v>
       </c>
       <c r="G726" s="1" t="s">
         <v>12</v>
@@ -21596,7 +21596,7 @@
         <v>13</v>
       </c>
       <c r="I726" s="4">
-        <v>2407</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="727" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21613,10 +21613,10 @@
         <v>11</v>
       </c>
       <c r="E727" s="2">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="F727" s="3">
-        <v>45764</v>
+        <v>45776</v>
       </c>
       <c r="G727" s="1" t="s">
         <v>12</v>
@@ -21625,7 +21625,7 @@
         <v>13</v>
       </c>
       <c r="I727" s="4">
-        <v>2503</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="728" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21642,10 +21642,10 @@
         <v>11</v>
       </c>
       <c r="E728" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F728" s="3">
-        <v>45776</v>
+        <v>45779</v>
       </c>
       <c r="G728" s="1" t="s">
         <v>12</v>
@@ -21654,7 +21654,7 @@
         <v>13</v>
       </c>
       <c r="I728" s="4">
-        <v>2412</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="729" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21674,7 +21674,7 @@
         <v>100</v>
       </c>
       <c r="F729" s="3">
-        <v>45779</v>
+        <v>45786</v>
       </c>
       <c r="G729" s="1" t="s">
         <v>12</v>
@@ -21683,7 +21683,7 @@
         <v>13</v>
       </c>
       <c r="I729" s="4">
-        <v>2407</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="730" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21694,25 +21694,25 @@
         <v>15</v>
       </c>
       <c r="C730" s="2">
-        <v>33.9</v>
+        <v>32.5</v>
       </c>
       <c r="D730" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E730" s="2">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F730" s="3">
-        <v>45786</v>
+        <v>45797</v>
       </c>
       <c r="G730" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H730" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I730" s="4">
-        <v>2503</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="731" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21723,25 +21723,25 @@
         <v>15</v>
       </c>
       <c r="C731" s="2">
-        <v>32.5</v>
+        <v>34.9</v>
       </c>
       <c r="D731" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E731" s="2">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="F731" s="3">
-        <v>45797</v>
+        <v>45799</v>
       </c>
       <c r="G731" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H731" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I731" s="4">
-        <v>2412</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="732" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21758,10 +21758,10 @@
         <v>11</v>
       </c>
       <c r="E732" s="2">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="F732" s="3">
-        <v>45799</v>
+        <v>45805</v>
       </c>
       <c r="G732" s="1" t="s">
         <v>12</v>
@@ -21770,7 +21770,7 @@
         <v>13</v>
       </c>
       <c r="I732" s="4">
-        <v>2317</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="733" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21787,10 +21787,10 @@
         <v>11</v>
       </c>
       <c r="E733" s="2">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="F733" s="3">
-        <v>45805</v>
+        <v>45806</v>
       </c>
       <c r="G733" s="1" t="s">
         <v>12</v>
@@ -21799,7 +21799,7 @@
         <v>13</v>
       </c>
       <c r="I733" s="4">
-        <v>2413</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="734" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21816,7 +21816,7 @@
         <v>11</v>
       </c>
       <c r="E734" s="2">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F734" s="3">
         <v>45806</v>
@@ -21828,7 +21828,7 @@
         <v>13</v>
       </c>
       <c r="I734" s="4">
-        <v>2412</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="735" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21839,22 +21839,22 @@
         <v>15</v>
       </c>
       <c r="C735" s="2">
-        <v>34.9</v>
+        <v>32.5</v>
       </c>
       <c r="D735" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E735" s="2">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F735" s="3">
-        <v>45806</v>
+        <v>45813</v>
       </c>
       <c r="G735" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H735" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I735" s="4">
         <v>2503</v>
@@ -21868,25 +21868,25 @@
         <v>15</v>
       </c>
       <c r="C736" s="2">
-        <v>32.5</v>
+        <v>34.9</v>
       </c>
       <c r="D736" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E736" s="2">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="F736" s="3">
-        <v>45813</v>
+        <v>45817</v>
       </c>
       <c r="G736" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H736" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I736" s="4">
-        <v>2503</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="737" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21903,10 +21903,10 @@
         <v>11</v>
       </c>
       <c r="E737" s="2">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="F737" s="3">
-        <v>45817</v>
+        <v>45819</v>
       </c>
       <c r="G737" s="1" t="s">
         <v>12</v>
@@ -21915,7 +21915,7 @@
         <v>13</v>
       </c>
       <c r="I737" s="4">
-        <v>2413</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="738" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21932,10 +21932,10 @@
         <v>11</v>
       </c>
       <c r="E738" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F738" s="3">
-        <v>45819</v>
+        <v>45821</v>
       </c>
       <c r="G738" s="1" t="s">
         <v>12</v>
@@ -21944,7 +21944,7 @@
         <v>13</v>
       </c>
       <c r="I738" s="4">
-        <v>2412</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="739" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21961,10 +21961,10 @@
         <v>11</v>
       </c>
       <c r="E739" s="2">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F739" s="3">
-        <v>45821</v>
+        <v>45827</v>
       </c>
       <c r="G739" s="1" t="s">
         <v>12</v>
@@ -21973,7 +21973,7 @@
         <v>13</v>
       </c>
       <c r="I739" s="4">
-        <v>2503</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="740" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21990,10 +21990,10 @@
         <v>11</v>
       </c>
       <c r="E740" s="2">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="F740" s="3">
-        <v>45827</v>
+        <v>45832</v>
       </c>
       <c r="G740" s="1" t="s">
         <v>12</v>
@@ -22002,7 +22002,7 @@
         <v>13</v>
       </c>
       <c r="I740" s="4">
-        <v>2317</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="741" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22019,10 +22019,10 @@
         <v>11</v>
       </c>
       <c r="E741" s="2">
-        <v>30</v>
+        <v>600</v>
       </c>
       <c r="F741" s="3">
-        <v>45832</v>
+        <v>45838</v>
       </c>
       <c r="G741" s="1" t="s">
         <v>12</v>
@@ -22031,7 +22031,7 @@
         <v>13</v>
       </c>
       <c r="I741" s="4">
-        <v>2413</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="742" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22048,7 +22048,7 @@
         <v>11</v>
       </c>
       <c r="E742" s="2">
-        <v>600</v>
+        <v>30</v>
       </c>
       <c r="F742" s="3">
         <v>45838</v>
@@ -22057,10 +22057,10 @@
         <v>12</v>
       </c>
       <c r="H742" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I742" s="4">
-        <v>2317</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="743" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22071,25 +22071,25 @@
         <v>15</v>
       </c>
       <c r="C743" s="2">
-        <v>34.9</v>
+        <v>34.5</v>
       </c>
       <c r="D743" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E743" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F743" s="3">
-        <v>45838</v>
+        <v>45840</v>
       </c>
       <c r="G743" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H743" s="1" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I743" s="4">
-        <v>2413</v>
+        <v>9987</v>
       </c>
     </row>
     <row r="744" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22106,7 +22106,7 @@
         <v>11</v>
       </c>
       <c r="E744" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F744" s="3">
         <v>45840</v>
@@ -22129,25 +22129,25 @@
         <v>15</v>
       </c>
       <c r="C745" s="2">
-        <v>34.5</v>
+        <v>34.9</v>
       </c>
       <c r="D745" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E745" s="2">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="F745" s="3">
-        <v>45840</v>
+        <v>45853</v>
       </c>
       <c r="G745" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H745" s="1" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="I745" s="4">
-        <v>9987</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="746" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22158,25 +22158,25 @@
         <v>15</v>
       </c>
       <c r="C746" s="2">
-        <v>34.9</v>
+        <v>34.5</v>
       </c>
       <c r="D746" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E746" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F746" s="3">
-        <v>45853</v>
+        <v>45854</v>
       </c>
       <c r="G746" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H746" s="1" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="I746" s="4">
-        <v>2413</v>
+        <v>9987</v>
       </c>
     </row>
     <row r="747" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22193,7 +22193,7 @@
         <v>11</v>
       </c>
       <c r="E747" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F747" s="3">
         <v>45854</v>
@@ -22222,19 +22222,19 @@
         <v>11</v>
       </c>
       <c r="E748" s="2">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="F748" s="3">
-        <v>45854</v>
+        <v>45860</v>
       </c>
       <c r="G748" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H748" s="1" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="I748" s="4">
-        <v>9987</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="749" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22251,10 +22251,10 @@
         <v>11</v>
       </c>
       <c r="E749" s="2">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="F749" s="3">
-        <v>45860</v>
+        <v>45919</v>
       </c>
       <c r="G749" s="1" t="s">
         <v>12</v>
@@ -22263,7 +22263,7 @@
         <v>13</v>
       </c>
       <c r="I749" s="4">
-        <v>2317</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="750" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22274,16 +22274,16 @@
         <v>15</v>
       </c>
       <c r="C750" s="2">
-        <v>34.5</v>
+        <v>36.9</v>
       </c>
       <c r="D750" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E750" s="2">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F750" s="3">
-        <v>45919</v>
+        <v>45957</v>
       </c>
       <c r="G750" s="1" t="s">
         <v>12</v>
@@ -22303,16 +22303,16 @@
         <v>15</v>
       </c>
       <c r="C751" s="2">
-        <v>36.9</v>
+        <v>34.5</v>
       </c>
       <c r="D751" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E751" s="2">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F751" s="3">
-        <v>45957</v>
+        <v>45979</v>
       </c>
       <c r="G751" s="1" t="s">
         <v>12</v>
@@ -22341,7 +22341,7 @@
         <v>50</v>
       </c>
       <c r="F752" s="3">
-        <v>45979</v>
+        <v>45988</v>
       </c>
       <c r="G752" s="1" t="s">
         <v>12</v>
@@ -22370,7 +22370,7 @@
         <v>50</v>
       </c>
       <c r="F753" s="3">
-        <v>45988</v>
+        <v>45994</v>
       </c>
       <c r="G753" s="1" t="s">
         <v>12</v>
@@ -22379,7 +22379,7 @@
         <v>13</v>
       </c>
       <c r="I753" s="4">
-        <v>2512</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="754" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22396,10 +22396,10 @@
         <v>11</v>
       </c>
       <c r="E754" s="2">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F754" s="3">
-        <v>45994</v>
+        <v>46002</v>
       </c>
       <c r="G754" s="1" t="s">
         <v>12</v>
@@ -22408,7 +22408,7 @@
         <v>13</v>
       </c>
       <c r="I754" s="4">
-        <v>2516</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="755" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22425,10 +22425,10 @@
         <v>11</v>
       </c>
       <c r="E755" s="2">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F755" s="3">
-        <v>46002</v>
+        <v>46009</v>
       </c>
       <c r="G755" s="1" t="s">
         <v>12</v>
@@ -22437,7 +22437,7 @@
         <v>13</v>
       </c>
       <c r="I755" s="4">
-        <v>2511</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="756" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22448,16 +22448,16 @@
         <v>15</v>
       </c>
       <c r="C756" s="2">
-        <v>34.5</v>
+        <v>34.9</v>
       </c>
       <c r="D756" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E756" s="2">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F756" s="3">
-        <v>46009</v>
+        <v>46029</v>
       </c>
       <c r="G756" s="1" t="s">
         <v>12</v>
@@ -22486,7 +22486,7 @@
         <v>100</v>
       </c>
       <c r="F757" s="3">
-        <v>46029</v>
+        <v>46036</v>
       </c>
       <c r="G757" s="1" t="s">
         <v>12</v>
@@ -22506,16 +22506,16 @@
         <v>15</v>
       </c>
       <c r="C758" s="2">
-        <v>34.9</v>
+        <v>34.5</v>
       </c>
       <c r="D758" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E758" s="2">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="F758" s="3">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="G758" s="1" t="s">
         <v>12</v>
@@ -22524,7 +22524,7 @@
         <v>13</v>
       </c>
       <c r="I758" s="4">
-        <v>2512</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="759" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22541,10 +22541,10 @@
         <v>11</v>
       </c>
       <c r="E759" s="2">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F759" s="3">
-        <v>46037</v>
+        <v>46045</v>
       </c>
       <c r="G759" s="1" t="s">
         <v>12</v>
@@ -22553,7 +22553,7 @@
         <v>13</v>
       </c>
       <c r="I759" s="4">
-        <v>2516</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="760" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22573,7 +22573,7 @@
         <v>50</v>
       </c>
       <c r="F760" s="3">
-        <v>46045</v>
+        <v>46055</v>
       </c>
       <c r="G760" s="1" t="s">
         <v>12</v>
@@ -22582,7 +22582,7 @@
         <v>13</v>
       </c>
       <c r="I760" s="4">
-        <v>2512</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="761" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22599,10 +22599,10 @@
         <v>11</v>
       </c>
       <c r="E761" s="2">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="F761" s="3">
-        <v>46055</v>
+        <v>46062</v>
       </c>
       <c r="G761" s="1" t="s">
         <v>12</v>
@@ -22611,7 +22611,7 @@
         <v>13</v>
       </c>
       <c r="I761" s="4">
-        <v>2516</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="762" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22628,10 +22628,10 @@
         <v>11</v>
       </c>
       <c r="E762" s="2">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F762" s="3">
-        <v>46062</v>
+        <v>46065</v>
       </c>
       <c r="G762" s="1" t="s">
         <v>12</v>
@@ -22640,7 +22640,7 @@
         <v>13</v>
       </c>
       <c r="I762" s="4">
-        <v>2512</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="763" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22657,10 +22657,10 @@
         <v>11</v>
       </c>
       <c r="E763" s="2">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="F763" s="3">
-        <v>46065</v>
+        <v>46072</v>
       </c>
       <c r="G763" s="1" t="s">
         <v>12</v>
@@ -22669,7 +22669,7 @@
         <v>13</v>
       </c>
       <c r="I763" s="4">
-        <v>2516</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="764" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22686,10 +22686,10 @@
         <v>11</v>
       </c>
       <c r="E764" s="2">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="F764" s="3">
-        <v>46072</v>
+        <v>46076</v>
       </c>
       <c r="G764" s="1" t="s">
         <v>12</v>
@@ -22698,7 +22698,7 @@
         <v>13</v>
       </c>
       <c r="I764" s="4">
-        <v>2407</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="765" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22715,10 +22715,10 @@
         <v>11</v>
       </c>
       <c r="E765" s="2">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F765" s="3">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="G765" s="1" t="s">
         <v>12</v>
@@ -22727,7 +22727,7 @@
         <v>13</v>
       </c>
       <c r="I765" s="4">
-        <v>2512</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="766" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22747,7 +22747,7 @@
         <v>50</v>
       </c>
       <c r="F766" s="3">
-        <v>46077</v>
+        <v>46083</v>
       </c>
       <c r="G766" s="1" t="s">
         <v>12</v>
@@ -22773,10 +22773,10 @@
         <v>11</v>
       </c>
       <c r="E767" s="2">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F767" s="3">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="G767" s="1" t="s">
         <v>12</v>
@@ -22785,7 +22785,7 @@
         <v>13</v>
       </c>
       <c r="I767" s="4">
-        <v>2516</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="768" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22796,7 +22796,7 @@
         <v>15</v>
       </c>
       <c r="C768" s="2">
-        <v>34.5</v>
+        <v>36.5</v>
       </c>
       <c r="D768" s="1" t="s">
         <v>11</v>
@@ -22805,7 +22805,7 @@
         <v>30</v>
       </c>
       <c r="F768" s="3">
-        <v>46084</v>
+        <v>46094</v>
       </c>
       <c r="G768" s="1" t="s">
         <v>12</v>
@@ -22814,7 +22814,7 @@
         <v>13</v>
       </c>
       <c r="I768" s="4">
-        <v>2512</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="769" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22825,16 +22825,16 @@
         <v>15</v>
       </c>
       <c r="C769" s="2">
-        <v>36.5</v>
+        <v>34.5</v>
       </c>
       <c r="D769" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E769" s="2">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F769" s="3">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="G769" s="1" t="s">
         <v>12</v>
@@ -22854,7 +22854,7 @@
         <v>15</v>
       </c>
       <c r="C770" s="2">
-        <v>34.5</v>
+        <v>36.5</v>
       </c>
       <c r="D770" s="1" t="s">
         <v>11</v>
@@ -22863,7 +22863,7 @@
         <v>50</v>
       </c>
       <c r="F770" s="3">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="G770" s="1" t="s">
         <v>12</v>
@@ -22883,16 +22883,16 @@
         <v>15</v>
       </c>
       <c r="C771" s="2">
-        <v>36.5</v>
+        <v>32.82</v>
       </c>
       <c r="D771" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E771" s="2">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F771" s="3">
-        <v>46098</v>
+        <v>46108</v>
       </c>
       <c r="G771" s="1" t="s">
         <v>12</v>
@@ -22912,16 +22912,16 @@
         <v>15</v>
       </c>
       <c r="C772" s="2">
-        <v>32.82</v>
+        <v>38.9</v>
       </c>
       <c r="D772" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E772" s="2">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="F772" s="3">
-        <v>46108</v>
+        <v>46118</v>
       </c>
       <c r="G772" s="1" t="s">
         <v>12</v>
@@ -22941,16 +22941,16 @@
         <v>15</v>
       </c>
       <c r="C773" s="2">
-        <v>38.9</v>
+        <v>38.5</v>
       </c>
       <c r="D773" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E773" s="2">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="F773" s="3">
-        <v>46118</v>
+        <v>46121</v>
       </c>
       <c r="G773" s="1" t="s">
         <v>12</v>
@@ -22959,7 +22959,7 @@
         <v>13</v>
       </c>
       <c r="I773" s="4">
-        <v>2516</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="774" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22970,16 +22970,16 @@
         <v>15</v>
       </c>
       <c r="C774" s="2">
-        <v>38.5</v>
+        <v>36.9</v>
       </c>
       <c r="D774" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E774" s="2">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F774" s="3">
-        <v>46121</v>
+        <v>46134</v>
       </c>
       <c r="G774" s="1" t="s">
         <v>12</v>
@@ -22988,7 +22988,7 @@
         <v>13</v>
       </c>
       <c r="I774" s="4">
-        <v>2512</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="775" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22999,25 +22999,25 @@
         <v>15</v>
       </c>
       <c r="C775" s="2">
-        <v>36.9</v>
+        <v>38.5</v>
       </c>
       <c r="D775" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E775" s="2">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F775" s="3">
-        <v>46134</v>
+        <v>46139</v>
       </c>
       <c r="G775" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H775" s="1" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="I775" s="4">
-        <v>2516</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="776" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23028,25 +23028,25 @@
         <v>15</v>
       </c>
       <c r="C776" s="2">
-        <v>38.5</v>
+        <v>38.9</v>
       </c>
       <c r="D776" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E776" s="2">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F776" s="3">
-        <v>46139</v>
+        <v>46142</v>
       </c>
       <c r="G776" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H776" s="1" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="I776" s="4">
-        <v>2511</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="777" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23057,16 +23057,16 @@
         <v>15</v>
       </c>
       <c r="C777" s="2">
-        <v>38.9</v>
+        <v>38.5</v>
       </c>
       <c r="D777" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E777" s="2">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="F777" s="3">
-        <v>46142</v>
+        <v>46153</v>
       </c>
       <c r="G777" s="1" t="s">
         <v>12</v>
@@ -23075,7 +23075,7 @@
         <v>13</v>
       </c>
       <c r="I777" s="4">
-        <v>2601</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="778" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23086,16 +23086,16 @@
         <v>15</v>
       </c>
       <c r="C778" s="2">
-        <v>38.5</v>
+        <v>36.9</v>
       </c>
       <c r="D778" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E778" s="2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F778" s="3">
-        <v>46153</v>
+        <v>46174</v>
       </c>
       <c r="G778" s="1" t="s">
         <v>12</v>
@@ -23104,7 +23104,7 @@
         <v>13</v>
       </c>
       <c r="I778" s="4">
-        <v>2512</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="779" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23115,7 +23115,7 @@
         <v>15</v>
       </c>
       <c r="C779" s="2">
-        <v>36.9</v>
+        <v>38.9</v>
       </c>
       <c r="D779" s="1" t="s">
         <v>11</v>
@@ -23124,7 +23124,7 @@
         <v>20</v>
       </c>
       <c r="F779" s="3">
-        <v>46174</v>
+        <v>46188</v>
       </c>
       <c r="G779" s="1" t="s">
         <v>12</v>
@@ -23144,16 +23144,16 @@
         <v>15</v>
       </c>
       <c r="C780" s="2">
-        <v>38.9</v>
+        <v>36.83</v>
       </c>
       <c r="D780" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E780" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F780" s="3">
-        <v>46188</v>
+        <v>46225</v>
       </c>
       <c r="G780" s="1" t="s">
         <v>12</v>
@@ -23162,7 +23162,7 @@
         <v>13</v>
       </c>
       <c r="I780" s="4">
-        <v>2516</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="781" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23173,16 +23173,16 @@
         <v>15</v>
       </c>
       <c r="C781" s="2">
-        <v>36.83</v>
+        <v>36.9</v>
       </c>
       <c r="D781" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E781" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="F781" s="3">
-        <v>46225</v>
+        <v>46234</v>
       </c>
       <c r="G781" s="1" t="s">
         <v>12</v>
@@ -23191,7 +23191,7 @@
         <v>13</v>
       </c>
       <c r="I781" s="4">
-        <v>2605</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="782" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23211,7 +23211,7 @@
         <v>20</v>
       </c>
       <c r="F782" s="3">
-        <v>46234</v>
+        <v>46245</v>
       </c>
       <c r="G782" s="1" t="s">
         <v>12</v>
@@ -23231,16 +23231,16 @@
         <v>15</v>
       </c>
       <c r="C783" s="2">
-        <v>36.9</v>
+        <v>39.9</v>
       </c>
       <c r="D783" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E783" s="2">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F783" s="3">
-        <v>46245</v>
+        <v>46248</v>
       </c>
       <c r="G783" s="1" t="s">
         <v>12</v>
@@ -23249,7 +23249,7 @@
         <v>13</v>
       </c>
       <c r="I783" s="4">
-        <v>2602</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="784" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23260,25 +23260,25 @@
         <v>15</v>
       </c>
       <c r="C784" s="2">
-        <v>39.9</v>
+        <v>35.5</v>
       </c>
       <c r="D784" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E784" s="2">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F784" s="3">
-        <v>46248</v>
+        <v>46254</v>
       </c>
       <c r="G784" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H784" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I784" s="4">
-        <v>2605</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="785" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23295,10 +23295,10 @@
         <v>11</v>
       </c>
       <c r="E785" s="2">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F785" s="3">
-        <v>46254</v>
+        <v>46259</v>
       </c>
       <c r="G785" s="1" t="s">
         <v>12</v>
@@ -23307,7 +23307,7 @@
         <v>16</v>
       </c>
       <c r="I785" s="4">
-        <v>2601</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="786" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23318,13 +23318,13 @@
         <v>15</v>
       </c>
       <c r="C786" s="2">
-        <v>35.5</v>
+        <v>34.82</v>
       </c>
       <c r="D786" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E786" s="2">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="F786" s="3">
         <v>46259</v>
@@ -23333,10 +23333,10 @@
         <v>12</v>
       </c>
       <c r="H786" s="1" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="I786" s="4">
-        <v>2605</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="787" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23347,25 +23347,25 @@
         <v>15</v>
       </c>
       <c r="C787" s="2">
-        <v>34.82</v>
+        <v>45</v>
       </c>
       <c r="D787" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E787" s="2">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="F787" s="3">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="G787" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H787" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I787" s="4">
-        <v>2606</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="788" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23376,25 +23376,25 @@
         <v>15</v>
       </c>
       <c r="C788" s="2">
-        <v>45</v>
+        <v>35.5</v>
       </c>
       <c r="D788" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E788" s="2">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F788" s="3">
-        <v>46261</v>
+        <v>46276</v>
       </c>
       <c r="G788" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H788" s="1" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="I788" s="4">
-        <v>2602</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="789" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23405,13 +23405,13 @@
         <v>15</v>
       </c>
       <c r="C789" s="2">
-        <v>35.5</v>
+        <v>36.9</v>
       </c>
       <c r="D789" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E789" s="2">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F789" s="3">
         <v>46276</v>
@@ -23420,10 +23420,10 @@
         <v>12</v>
       </c>
       <c r="H789" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I789" s="4">
-        <v>2601</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="790" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23434,16 +23434,16 @@
         <v>15</v>
       </c>
       <c r="C790" s="2">
-        <v>36.9</v>
+        <v>39.9</v>
       </c>
       <c r="D790" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E790" s="2">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="F790" s="3">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="G790" s="1" t="s">
         <v>12</v>
@@ -23452,7 +23452,7 @@
         <v>13</v>
       </c>
       <c r="I790" s="4">
-        <v>2612</v>
+        <v>2605</v>
       </c>
     </row>
     <row r="791" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23463,16 +23463,16 @@
         <v>15</v>
       </c>
       <c r="C791" s="2">
-        <v>39.9</v>
+        <v>39.96</v>
       </c>
       <c r="D791" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E791" s="2">
-        <v>250</v>
+        <v>5</v>
       </c>
       <c r="F791" s="3">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="G791" s="1" t="s">
         <v>12</v>
@@ -23481,7 +23481,7 @@
         <v>13</v>
       </c>
       <c r="I791" s="4">
-        <v>2605</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="792" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23492,25 +23492,25 @@
         <v>15</v>
       </c>
       <c r="C792" s="2">
-        <v>39.96</v>
+        <v>35.53</v>
       </c>
       <c r="D792" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E792" s="2">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="F792" s="3">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="G792" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H792" s="1" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="I792" s="4">
-        <v>2602</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="793" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23521,25 +23521,25 @@
         <v>15</v>
       </c>
       <c r="C793" s="2">
-        <v>35.53</v>
+        <v>35.5</v>
       </c>
       <c r="D793" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E793" s="2">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="F793" s="3">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="G793" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H793" s="1" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="I793" s="4">
-        <v>2606</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="794" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23556,10 +23556,10 @@
         <v>11</v>
       </c>
       <c r="E794" s="2">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F794" s="3">
-        <v>46283</v>
+        <v>46289</v>
       </c>
       <c r="G794" s="1" t="s">
         <v>12</v>
@@ -23568,35 +23568,6 @@
         <v>16</v>
       </c>
       <c r="I794" s="4">
-        <v>2601</v>
-      </c>
-    </row>
-    <row r="795" spans="1:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A795" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B795" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C795" s="2">
-        <v>35.5</v>
-      </c>
-      <c r="D795" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E795" s="2">
-        <v>100</v>
-      </c>
-      <c r="F795" s="3">
-        <v>46289</v>
-      </c>
-      <c r="G795" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H795" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I795" s="4">
         <v>2612</v>
       </c>
     </row>

--- a/BaseInflação.xlsx
+++ b/BaseInflação.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://osborne1-my.sharepoint.com/personal/antonio_macedo_osborne_com_br/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="13_ncr:1_{6FEE0F3F-AAF6-4BEC-810F-C57612871236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06D55776-F77F-4DC9-B550-A67FBCA15BA5}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="13_ncr:1_{6FEE0F3F-AAF6-4BEC-810F-C57612871236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F247A3E-8667-4EEA-B06D-65BE227F57DF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10558,7 +10558,7 @@
         <v>36</v>
       </c>
       <c r="C346" s="2">
-        <v>49.81</v>
+        <v>6.75</v>
       </c>
       <c r="D346" s="1" t="s">
         <v>37</v>
@@ -10587,7 +10587,7 @@
         <v>36</v>
       </c>
       <c r="C347" s="2">
-        <v>49.81</v>
+        <v>6.8</v>
       </c>
       <c r="D347" s="1" t="s">
         <v>37</v>
@@ -10616,7 +10616,7 @@
         <v>36</v>
       </c>
       <c r="C348" s="2">
-        <v>52.25</v>
+        <v>6.85</v>
       </c>
       <c r="D348" s="1" t="s">
         <v>37</v>
@@ -10645,7 +10645,7 @@
         <v>36</v>
       </c>
       <c r="C349" s="2">
-        <v>43.48</v>
+        <v>6.8</v>
       </c>
       <c r="D349" s="1" t="s">
         <v>37</v>
@@ -10674,7 +10674,7 @@
         <v>36</v>
       </c>
       <c r="C350" s="2">
-        <v>49.81</v>
+        <v>6.95</v>
       </c>
       <c r="D350" s="1" t="s">
         <v>37</v>
@@ -10703,7 +10703,7 @@
         <v>36</v>
       </c>
       <c r="C351" s="2">
-        <v>49.81</v>
+        <v>7.9</v>
       </c>
       <c r="D351" s="1" t="s">
         <v>37</v>
